--- a/data/TDS.xlsx
+++ b/data/TDS.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="1025">
   <si>
     <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-ELASTOFLEX-7492.pdf</t>
   </si>
@@ -2724,13 +2724,388 @@
   </si>
   <si>
     <t>Hind Fix TA – type 3</t>
+  </si>
+  <si>
+    <t>EXPANSION TAPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPANSION TAPE ADHESIVE </t>
+  </si>
+  <si>
+    <t>GEO POLYMER CONCRETE ADMIXTURE</t>
+  </si>
+  <si>
+    <t>GLOSSY ADMIXTURE</t>
+  </si>
+  <si>
+    <t>PU COATING</t>
+  </si>
+  <si>
+    <t>BUTYL TAPE</t>
+  </si>
+  <si>
+    <t>POLYCARBOXYLATE ETHER</t>
+  </si>
+  <si>
+    <t>PU CONCRETE FLOORING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PU COATING </t>
+  </si>
+  <si>
+    <t>REPEL</t>
+  </si>
+  <si>
+    <t>CRACK SEALANT</t>
+  </si>
+  <si>
+    <t>GLITTER</t>
+  </si>
+  <si>
+    <t>SELF LEVELLING CEMENTIOUS ADMIXTURE</t>
+  </si>
+  <si>
+    <t>E3-G-IN</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/E3-G-IN.pdf</t>
+  </si>
+  <si>
+    <t>HYD500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-HYD-500-1.pdf</t>
+  </si>
+  <si>
+    <t>HBD500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HBD500.pdf</t>
+  </si>
+  <si>
+    <t>HIND ERS 11</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-ERS-11.pdf</t>
+  </si>
+  <si>
+    <t>HIND ERS 2112</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-ERS-2112.pdf</t>
+  </si>
+  <si>
+    <t>HIND HYPER FLUID 6706</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-HYPER-FLUID-6706.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PU ADHESIVE </t>
+  </si>
+  <si>
+    <t>HIND PU MASTERFLEX 512A</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-PU-MASTERFLEX-512A.pdf</t>
+  </si>
+  <si>
+    <t>PU PUTTY</t>
+  </si>
+  <si>
+    <t>HIND PU PYT 760</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-PU-PYT-760.pdf</t>
+  </si>
+  <si>
+    <t>HIND RV 40</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-RV-40.pdf</t>
+  </si>
+  <si>
+    <t>SUPER FINE</t>
+  </si>
+  <si>
+    <t>Hind Superfine 5209</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/Hind-Superfine-5209.pdf</t>
+  </si>
+  <si>
+    <t>LATEX BOND</t>
+  </si>
+  <si>
+    <t>HIND ULTRA BOND 1202</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-ULTRA-BOND-1202.pdf</t>
+  </si>
+  <si>
+    <t>Hindcon Chemicals Limited</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/Hindcon-Chemicals-Limited.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT HD 500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-HD-500.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT HD 700</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-HD-700.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT HRC 500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-HRC-500.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT HWD 500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-HWD-500.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT SD 500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-SD-500.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT SR 50</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-SR-50.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT SRF 50</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-SRF-50-1.pdf</t>
+  </si>
+  <si>
+    <t>HYDROSOFT WD 500</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/HYDROSOFT-WD-500.pdf</t>
+  </si>
+  <si>
+    <t>REPEL BOND +</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/REPEL-BOND-.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SODIUM METASILICATE </t>
+  </si>
+  <si>
+    <t>SODIUM METASILICATE NONAHYDRATE</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/SODIUM-METASILICATE-NONAHYDRATE.pdf</t>
+  </si>
+  <si>
+    <t>SODIUM METASILICATE PENTAHYDRATE</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/SODIUM-METASILICATE-PENTAHYDRATE.pdf</t>
+  </si>
+  <si>
+    <t>Water-Based Primer</t>
+  </si>
+  <si>
+    <t>https://www.hindcon.com/wp-content/uploads/2026/09/Water-Based-Primer.pdf</t>
+  </si>
+  <si>
+    <t>HC321</t>
+  </si>
+  <si>
+    <t>HC322</t>
+  </si>
+  <si>
+    <t>HC323</t>
+  </si>
+  <si>
+    <t>HC324</t>
+  </si>
+  <si>
+    <t>HC325</t>
+  </si>
+  <si>
+    <t>HC326</t>
+  </si>
+  <si>
+    <t>HC327</t>
+  </si>
+  <si>
+    <t>HC328</t>
+  </si>
+  <si>
+    <t>HC329</t>
+  </si>
+  <si>
+    <t>HC330</t>
+  </si>
+  <si>
+    <t>HC331</t>
+  </si>
+  <si>
+    <t>HC332</t>
+  </si>
+  <si>
+    <t>HC333</t>
+  </si>
+  <si>
+    <t>HC334</t>
+  </si>
+  <si>
+    <t>HC335</t>
+  </si>
+  <si>
+    <t>HC336</t>
+  </si>
+  <si>
+    <t>HC337</t>
+  </si>
+  <si>
+    <t>HC338</t>
+  </si>
+  <si>
+    <t>HC339</t>
+  </si>
+  <si>
+    <t>HC340</t>
+  </si>
+  <si>
+    <t>HC341</t>
+  </si>
+  <si>
+    <t>HC342</t>
+  </si>
+  <si>
+    <t>HC343</t>
+  </si>
+  <si>
+    <t>HC344</t>
+  </si>
+  <si>
+    <t>HC345</t>
+  </si>
+  <si>
+    <t>HC346</t>
+  </si>
+  <si>
+    <t>HC347</t>
+  </si>
+  <si>
+    <t>HC348</t>
+  </si>
+  <si>
+    <t>HC349</t>
+  </si>
+  <si>
+    <t>HC350</t>
+  </si>
+  <si>
+    <t>HC351</t>
+  </si>
+  <si>
+    <t>HC352</t>
+  </si>
+  <si>
+    <t>HC353</t>
+  </si>
+  <si>
+    <t>HC354</t>
+  </si>
+  <si>
+    <t>HC355</t>
+  </si>
+  <si>
+    <t>HC356</t>
+  </si>
+  <si>
+    <t>HC357</t>
+  </si>
+  <si>
+    <t>HC358</t>
+  </si>
+  <si>
+    <t>HC359</t>
+  </si>
+  <si>
+    <t>HC360</t>
+  </si>
+  <si>
+    <t>HC361</t>
+  </si>
+  <si>
+    <t>HC362</t>
+  </si>
+  <si>
+    <t>HC363</t>
+  </si>
+  <si>
+    <t>HC364</t>
+  </si>
+  <si>
+    <t>HC365</t>
+  </si>
+  <si>
+    <t>HC366</t>
+  </si>
+  <si>
+    <t>HC367</t>
+  </si>
+  <si>
+    <t>HC368</t>
+  </si>
+  <si>
+    <t>HC369</t>
+  </si>
+  <si>
+    <t>HC370</t>
+  </si>
+  <si>
+    <t>HC371</t>
+  </si>
+  <si>
+    <t>HC372</t>
+  </si>
+  <si>
+    <t>HC373</t>
+  </si>
+  <si>
+    <t>HC374</t>
+  </si>
+  <si>
+    <t>HC375</t>
+  </si>
+  <si>
+    <t>HC376</t>
+  </si>
+  <si>
+    <t>HC377</t>
+  </si>
+  <si>
+    <t>HC378</t>
+  </si>
+  <si>
+    <t>HC379</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2768,7 +3143,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2776,29 +3151,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF333333"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2824,7 +3188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2847,134 +3211,77 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3256,4805 +3563,5594 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E381"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="93" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="84.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="38.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="84.5703125" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="22" t="s">
         <v>893</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>894</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="20" t="s">
         <v>895</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="23" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="17" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="17" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="17" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="17" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="17" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D48" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="31" t="s">
+      <c r="D49" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="31" t="s">
+      <c r="D50" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D51" s="31" t="s">
+      <c r="D51" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="31" t="s">
+      <c r="D53" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="31" t="s">
+      <c r="D54" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D55" s="31" t="s">
+      <c r="D55" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="31" t="s">
+      <c r="D56" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D57" s="30" t="s">
+      <c r="D57" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D58" s="30" t="s">
+      <c r="D58" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D59" s="30" t="s">
+      <c r="D59" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="30" t="s">
+      <c r="D60" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C63" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="D64" s="30" t="s">
+      <c r="D64" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D65" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D66" s="30" t="s">
+      <c r="D66" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="17" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D67" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="5"/>
-    </row>
-    <row r="68" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="E67" s="10"/>
+    </row>
+    <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D69" s="30" t="s">
+      <c r="D69" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="E69" s="5"/>
-    </row>
-    <row r="70" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="E69" s="10"/>
+    </row>
+    <row r="70" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D70" s="30" t="s">
+      <c r="D70" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="17" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="5"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D72" s="30" t="s">
+      <c r="D72" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="E72" s="5"/>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="D73" s="30" t="s">
+      <c r="D73" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="E73" s="5"/>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D74" s="30" t="s">
+      <c r="D74" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="17" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="21" t="s">
+      <c r="C75" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D75" s="30" t="s">
+      <c r="D75" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E75" s="5"/>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="21" t="s">
+      <c r="C76" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D76" s="30" t="s">
+      <c r="D76" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="E76" s="5"/>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D77" s="30" t="s">
+      <c r="D77" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="E77" s="5"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D78" s="30" t="s">
+      <c r="D78" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E78" s="5"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="C79" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D79" s="30" t="s">
+      <c r="D79" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="E79" s="5"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D80" s="30" t="s">
+      <c r="D80" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="E80" s="5"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D81" s="30" t="s">
+      <c r="D81" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E81" s="5"/>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D82" s="30" t="s">
+      <c r="D82" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="E82" s="5"/>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="24" t="s">
+      <c r="C83" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D83" s="30" t="s">
+      <c r="D83" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E83" s="5"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B84" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C84" s="24" t="s">
+      <c r="C84" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D84" s="30" t="s">
+      <c r="D84" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="E84" s="5"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C85" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="E85" s="5"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C86" s="24" t="s">
+      <c r="C86" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D86" s="30" t="s">
+      <c r="D86" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E86" s="5"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B87" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C87" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D87" s="30" t="s">
+      <c r="D87" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="E87" s="5"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C88" s="24" t="s">
+      <c r="C88" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D88" s="30" t="s">
+      <c r="D88" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="E88" s="5"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C89" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D89" s="31" t="s">
+      <c r="D89" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B90" s="16" t="s">
+      <c r="B90" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="22" t="s">
+      <c r="C90" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D90" s="31" t="s">
+      <c r="D90" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C91" s="22" t="s">
+      <c r="C91" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D91" s="31" t="s">
+      <c r="D91" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B92" s="16" t="s">
+      <c r="B92" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C92" s="22" t="s">
+      <c r="C92" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D92" s="31" t="s">
+      <c r="D92" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B93" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C93" s="22" t="s">
+      <c r="C93" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D93" s="31" t="s">
+      <c r="D93" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C94" s="22" t="s">
+      <c r="C94" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D94" s="31" t="s">
+      <c r="D94" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="22" t="s">
+      <c r="C95" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D95" s="31" t="s">
+      <c r="D95" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C96" s="21" t="s">
+      <c r="C96" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D96" s="30" t="s">
+      <c r="D96" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="E96" s="5"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="C97" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D97" s="30" t="s">
+      <c r="D97" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E97" s="17" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C98" s="21" t="s">
+      <c r="C98" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D98" s="30" t="s">
+      <c r="D98" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="E98" s="5"/>
+      <c r="E98" s="10"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C99" s="21" t="s">
+      <c r="C99" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D99" s="30" t="s">
+      <c r="D99" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="E99" s="5"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B100" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D100" s="30" t="s">
+      <c r="D100" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="E100" s="5"/>
+      <c r="E100" s="10"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D101" s="30" t="s">
+      <c r="D101" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="E101" s="5"/>
+      <c r="E101" s="10"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C102" s="21" t="s">
+      <c r="C102" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D102" s="30" t="s">
+      <c r="D102" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="E102" s="5"/>
+      <c r="E102" s="10"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B103" s="16" t="s">
+      <c r="B103" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C103" s="21" t="s">
+      <c r="C103" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D103" s="30" t="s">
+      <c r="D103" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="E103" s="5"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D104" s="30" t="s">
+      <c r="D104" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="E104" s="5"/>
+      <c r="E104" s="10"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D105" s="30" t="s">
+      <c r="D105" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="E105" s="5"/>
+      <c r="E105" s="10"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D106" s="30" t="s">
+      <c r="D106" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="E106" s="5"/>
+      <c r="E106" s="10"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C107" s="21" t="s">
+      <c r="C107" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D107" s="30" t="s">
+      <c r="D107" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="E107" s="5"/>
+      <c r="E107" s="10"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C108" s="21" t="s">
+      <c r="C108" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D108" s="30" t="s">
+      <c r="D108" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E108" s="5"/>
+      <c r="E108" s="10"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C109" s="21" t="s">
+      <c r="C109" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D109" s="30" t="s">
+      <c r="D109" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="E109" s="5"/>
+      <c r="E109" s="10"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B110" s="16" t="s">
+      <c r="B110" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D110" s="30" t="s">
+      <c r="D110" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="E110" s="5"/>
+      <c r="E110" s="10"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="D111" s="30" t="s">
+      <c r="D111" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="E111" s="5"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B112" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D112" s="30" t="s">
+      <c r="D112" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="E112" s="5"/>
+      <c r="E112" s="10"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="D113" s="30" t="s">
+      <c r="D113" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E113" s="5"/>
+      <c r="E113" s="10"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D114" s="30" t="s">
+      <c r="D114" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E114" s="17" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D115" s="30" t="s">
+      <c r="D115" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="E115" s="5"/>
+      <c r="E115" s="10"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="B116" s="16" t="s">
+      <c r="B116" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="D116" s="30" t="s">
+      <c r="D116" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E116" s="17" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="B117" s="16" t="s">
+      <c r="B117" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D117" s="30" t="s">
+      <c r="D117" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="E117" s="7"/>
+      <c r="E117" s="10"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B118" s="16" t="s">
+      <c r="B118" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D118" s="30" t="s">
+      <c r="D118" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E118" s="5"/>
+      <c r="E118" s="10"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="B119" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C119" s="21" t="s">
+      <c r="C119" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D119" s="30" t="s">
+      <c r="D119" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E119" s="5"/>
+      <c r="E119" s="10"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B120" s="16" t="s">
+      <c r="B120" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C120" s="21" t="s">
+      <c r="C120" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D120" s="30" t="s">
+      <c r="D120" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E120" s="5"/>
+      <c r="E120" s="10"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="B121" s="16" t="s">
+      <c r="B121" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C121" s="21" t="s">
+      <c r="C121" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D121" s="30" t="s">
+      <c r="D121" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E121" s="5"/>
+      <c r="E121" s="10"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="B122" s="16" t="s">
+      <c r="B122" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="D122" s="30" t="s">
+      <c r="D122" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" s="17" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B123" s="16" t="s">
+      <c r="B123" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="D123" s="30" t="s">
+      <c r="D123" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="E123" s="5"/>
+      <c r="E123" s="10"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="B124" s="16" t="s">
+      <c r="B124" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C124" s="21" t="s">
+      <c r="C124" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="D124" s="30" t="s">
+      <c r="D124" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E124" s="5"/>
+      <c r="E124" s="10"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="B125" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C125" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D125" s="30" t="s">
+      <c r="D125" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="E125" s="5"/>
+      <c r="E125" s="10"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B126" s="16" t="s">
+      <c r="B126" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C126" s="21" t="s">
+      <c r="C126" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D126" s="30" t="s">
+      <c r="D126" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="E126" s="5"/>
+      <c r="E126" s="10"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="B127" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C127" s="21" t="s">
+      <c r="C127" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="D127" s="30" t="s">
+      <c r="D127" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="E127" s="5"/>
+      <c r="E127" s="10"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B128" s="16" t="s">
+      <c r="B128" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C128" s="21" t="s">
+      <c r="C128" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="D128" s="30" t="s">
+      <c r="D128" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="E128" s="5"/>
+      <c r="E128" s="10"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B129" s="16" t="s">
+      <c r="B129" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="C129" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="D129" s="30" t="s">
+      <c r="D129" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="E129" s="5"/>
+      <c r="E129" s="10"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B130" s="16" t="s">
+      <c r="B130" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D130" s="30" t="s">
+      <c r="D130" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="E130" s="5"/>
+      <c r="E130" s="10"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="B131" s="16" t="s">
+      <c r="B131" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C131" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D131" s="30" t="s">
+      <c r="D131" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="E131" s="5"/>
+      <c r="E131" s="10"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B132" s="16" t="s">
+      <c r="B132" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C132" s="21" t="s">
+      <c r="C132" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="D132" s="30" t="s">
+      <c r="D132" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="E132" s="5"/>
+      <c r="E132" s="10"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="B133" s="16" t="s">
+      <c r="B133" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C133" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="D133" s="30" t="s">
+      <c r="D133" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E133" s="5"/>
+      <c r="E133" s="10"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="B134" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C134" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="D134" s="30" t="s">
+      <c r="D134" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="E134" s="5"/>
+      <c r="E134" s="10"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B135" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C135" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D135" s="30" t="s">
+      <c r="D135" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E135" s="5"/>
+      <c r="E135" s="10"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B136" s="16" t="s">
+      <c r="B136" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="C136" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="D136" s="30" t="s">
+      <c r="D136" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="E136" s="5"/>
+      <c r="E136" s="10"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C137" s="21" t="s">
+      <c r="C137" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D137" s="30" t="s">
+      <c r="D137" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="E137" s="5"/>
+      <c r="E137" s="10"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C138" s="21" t="s">
+      <c r="C138" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D138" s="30" t="s">
+      <c r="D138" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="E138" s="5"/>
+      <c r="E138" s="10"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D139" s="30" t="s">
+      <c r="D139" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="E139" s="5"/>
+      <c r="E139" s="10"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D140" s="30" t="s">
+      <c r="D140" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="E140" s="5"/>
+      <c r="E140" s="10"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C141" s="21" t="s">
+      <c r="C141" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D141" s="30" t="s">
+      <c r="D141" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="E141" s="5"/>
+      <c r="E141" s="10"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D142" s="30" t="s">
+      <c r="D142" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="E142" s="5"/>
+      <c r="E142" s="10"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B143" s="16" t="s">
+      <c r="B143" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C143" s="21" t="s">
+      <c r="C143" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D143" s="30" t="s">
+      <c r="D143" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="E143" s="5"/>
+      <c r="E143" s="10"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C144" s="21" t="s">
+      <c r="C144" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D144" s="30" t="s">
+      <c r="D144" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="E144" s="5"/>
+      <c r="E144" s="10"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C145" s="25" t="s">
+      <c r="C145" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="D145" s="30" t="s">
+      <c r="D145" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="E145" s="4" t="s">
+      <c r="E145" s="17" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C146" s="21" t="s">
+      <c r="C146" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="D146" s="30" t="s">
+      <c r="D146" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="E146" s="5"/>
+      <c r="E146" s="10"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C147" s="21" t="s">
+      <c r="C147" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D147" s="30" t="s">
+      <c r="D147" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="E147" s="5"/>
+      <c r="E147" s="10"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="B148" s="16" t="s">
+      <c r="B148" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C148" s="21" t="s">
+      <c r="C148" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="D148" s="30" t="s">
+      <c r="D148" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="E148" s="5"/>
+      <c r="E148" s="10"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B149" s="16" t="s">
+      <c r="B149" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C149" s="21" t="s">
+      <c r="C149" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="D149" s="30" t="s">
+      <c r="D149" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="E149" s="5"/>
+      <c r="E149" s="10"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C150" s="21" t="s">
+      <c r="C150" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D150" s="30" t="s">
+      <c r="D150" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="E150" s="5"/>
+      <c r="E150" s="10"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C151" s="21" t="s">
+      <c r="C151" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D151" s="30" t="s">
+      <c r="D151" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="E151" s="5"/>
+      <c r="E151" s="10"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C152" s="21" t="s">
+      <c r="C152" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D152" s="30" t="s">
+      <c r="D152" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="E152" s="5"/>
+      <c r="E152" s="10"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C153" s="21" t="s">
+      <c r="C153" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D153" s="30" t="s">
+      <c r="D153" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="E153" s="5"/>
+      <c r="E153" s="10"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="C154" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="D154" s="30" t="s">
+      <c r="D154" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="E154" s="5"/>
+      <c r="E154" s="10"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C155" s="21" t="s">
+      <c r="C155" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D155" s="30" t="s">
+      <c r="D155" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="17" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C156" s="21" t="s">
+      <c r="C156" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D156" s="30" t="s">
+      <c r="D156" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="E156" s="5"/>
+      <c r="E156" s="10"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C157" s="21" t="s">
+      <c r="C157" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D157" s="30" t="s">
+      <c r="D157" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="E157" s="5"/>
+      <c r="E157" s="10"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C158" s="21" t="s">
+      <c r="C158" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D158" s="30" t="s">
+      <c r="D158" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="E158" s="5"/>
+      <c r="E158" s="10"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B159" s="16" t="s">
+      <c r="B159" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C159" s="21" t="s">
+      <c r="C159" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="D159" s="30" t="s">
+      <c r="D159" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="E159" s="5"/>
+      <c r="E159" s="10"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="B160" s="17" t="s">
+      <c r="B160" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C160" s="22" t="s">
+      <c r="C160" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D160" s="31" t="s">
+      <c r="D160" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="B161" s="16" t="s">
+      <c r="B161" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C161" s="21" t="s">
+      <c r="C161" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D161" s="30" t="s">
+      <c r="D161" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="E161" s="5"/>
+      <c r="E161" s="10"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B162" s="16" t="s">
+      <c r="B162" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C162" s="21" t="s">
+      <c r="C162" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="D162" s="30" t="s">
+      <c r="D162" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="E162" s="5"/>
+      <c r="E162" s="10"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C163" s="21" t="s">
+      <c r="C163" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D163" s="30" t="s">
+      <c r="D163" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="E163" s="5"/>
+      <c r="E163" s="10"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="B164" s="16" t="s">
+      <c r="B164" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C164" s="21" t="s">
+      <c r="C164" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D164" s="30" t="s">
+      <c r="D164" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="E164" s="5"/>
+      <c r="E164" s="10"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="B165" s="16" t="s">
+      <c r="B165" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C165" s="21" t="s">
+      <c r="C165" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="D165" s="30" t="s">
+      <c r="D165" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="E165" s="5"/>
+      <c r="E165" s="10"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="B166" s="16" t="s">
+      <c r="B166" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C166" s="21" t="s">
+      <c r="C166" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D166" s="30" t="s">
+      <c r="D166" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="E166" s="5"/>
+      <c r="E166" s="10"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="B167" s="16" t="s">
+      <c r="B167" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C167" s="21" t="s">
+      <c r="C167" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D167" s="30" t="s">
+      <c r="D167" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="E167" s="5"/>
+      <c r="E167" s="10"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B168" s="16" t="s">
+      <c r="B168" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C168" s="21" t="s">
+      <c r="C168" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D168" s="30" t="s">
+      <c r="D168" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="E168" s="5"/>
+      <c r="E168" s="10"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B169" s="16" t="s">
+      <c r="B169" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C169" s="21" t="s">
+      <c r="C169" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="D169" s="30" t="s">
+      <c r="D169" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="E169" s="5"/>
+      <c r="E169" s="10"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B170" s="16" t="s">
+      <c r="B170" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C170" s="21" t="s">
+      <c r="C170" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D170" s="30" t="s">
+      <c r="D170" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="E170" s="5"/>
+      <c r="E170" s="10"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="B171" s="16" t="s">
+      <c r="B171" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C171" s="21" t="s">
+      <c r="C171" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="D171" s="30" t="s">
+      <c r="D171" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="E171" s="5"/>
+      <c r="E171" s="10"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B172" s="16" t="s">
+      <c r="B172" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C172" s="21" t="s">
+      <c r="C172" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="D172" s="30" t="s">
+      <c r="D172" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="E172" s="5"/>
+      <c r="E172" s="10"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="B173" s="16" t="s">
+      <c r="B173" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C173" s="21" t="s">
+      <c r="C173" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D173" s="30" t="s">
+      <c r="D173" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="E173" s="5"/>
+      <c r="E173" s="10"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B174" s="16" t="s">
+      <c r="B174" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C174" s="21" t="s">
+      <c r="C174" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D174" s="30" t="s">
+      <c r="D174" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="E174" s="5"/>
+      <c r="E174" s="10"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="B175" s="16" t="s">
+      <c r="B175" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C175" s="21" t="s">
+      <c r="C175" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="D175" s="30" t="s">
+      <c r="D175" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="E175" s="5"/>
+      <c r="E175" s="10"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="B176" s="16" t="s">
+      <c r="B176" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C176" s="23" t="s">
+      <c r="C176" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="D176" s="30" t="s">
+      <c r="D176" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="E176" s="5"/>
+      <c r="E176" s="10"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="B177" s="16" t="s">
+      <c r="B177" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C177" s="21" t="s">
+      <c r="C177" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D177" s="30" t="s">
+      <c r="D177" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="E177" s="5"/>
+      <c r="E177" s="10"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="B178" s="16" t="s">
+      <c r="B178" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C178" s="21" t="s">
+      <c r="C178" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="D178" s="30" t="s">
+      <c r="D178" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="E178" s="5"/>
+      <c r="E178" s="10"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="B179" s="16" t="s">
+      <c r="B179" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C179" s="21" t="s">
+      <c r="C179" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D179" s="30" t="s">
+      <c r="D179" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="E179" s="5"/>
+      <c r="E179" s="10"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="B180" s="16" t="s">
+      <c r="B180" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C180" s="21" t="s">
+      <c r="C180" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D180" s="30" t="s">
+      <c r="D180" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="E180" s="5"/>
+      <c r="E180" s="10"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="B181" s="16" t="s">
+      <c r="B181" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C181" s="21" t="s">
+      <c r="C181" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="D181" s="30" t="s">
+      <c r="D181" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="E181" s="5"/>
+      <c r="E181" s="10"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B182" s="16" t="s">
+      <c r="B182" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C182" s="21" t="s">
+      <c r="C182" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D182" s="30" t="s">
+      <c r="D182" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="E182" s="5"/>
+      <c r="E182" s="10"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="B183" s="17" t="s">
+      <c r="B183" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C183" s="22" t="s">
+      <c r="C183" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D183" s="31" t="s">
+      <c r="D183" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E183" s="1"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="B184" s="16" t="s">
+      <c r="B184" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C184" s="26" t="s">
+      <c r="C184" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D184" s="30" t="s">
+      <c r="D184" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="E184" s="5"/>
+      <c r="E184" s="10"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B185" s="16" t="s">
+      <c r="B185" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C185" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="D185" s="30" t="s">
+      <c r="D185" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="E185" s="5"/>
+      <c r="E185" s="10"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="B186" s="16" t="s">
+      <c r="B186" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C186" s="26" t="s">
+      <c r="C186" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D186" s="30" t="s">
+      <c r="D186" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="E186" s="5"/>
+      <c r="E186" s="10"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="B187" s="16" t="s">
+      <c r="B187" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C187" s="26" t="s">
+      <c r="C187" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="D187" s="30" t="s">
+      <c r="D187" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="E187" s="5"/>
+      <c r="E187" s="10"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="B188" s="16" t="s">
+      <c r="B188" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C188" s="26" t="s">
+      <c r="C188" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="D188" s="30" t="s">
+      <c r="D188" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="E188" s="5"/>
+      <c r="E188" s="10"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="B189" s="16" t="s">
+      <c r="B189" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C189" s="26" t="s">
+      <c r="C189" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="D189" s="30" t="s">
+      <c r="D189" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="E189" s="5"/>
+      <c r="E189" s="10"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B190" s="16" t="s">
+      <c r="B190" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C190" s="26" t="s">
+      <c r="C190" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D190" s="30" t="s">
+      <c r="D190" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="E190" s="5"/>
+      <c r="E190" s="10"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="B191" s="16" t="s">
+      <c r="B191" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C191" s="26" t="s">
+      <c r="C191" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="D191" s="30" t="s">
+      <c r="D191" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="E191" s="5"/>
+      <c r="E191" s="10"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B192" s="16" t="s">
+      <c r="B192" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C192" s="26" t="s">
+      <c r="C192" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D192" s="30" t="s">
+      <c r="D192" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="E192" s="5"/>
+      <c r="E192" s="10"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="B193" s="16" t="s">
+      <c r="B193" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C193" s="26" t="s">
+      <c r="C193" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="D193" s="30" t="s">
+      <c r="D193" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="E193" s="5"/>
+      <c r="E193" s="10"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="B194" s="16" t="s">
+      <c r="B194" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C194" s="13" t="s">
+      <c r="C194" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="D194" s="30" t="s">
+      <c r="D194" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="E194" s="5"/>
+      <c r="E194" s="10"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B195" s="16" t="s">
+      <c r="B195" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C195" s="13" t="s">
+      <c r="C195" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D195" s="30" t="s">
+      <c r="D195" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="E195" s="5"/>
+      <c r="E195" s="10"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B196" s="16" t="s">
+      <c r="B196" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C196" s="13" t="s">
+      <c r="C196" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="D196" s="30" t="s">
+      <c r="D196" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="E196" s="5"/>
+      <c r="E196" s="10"/>
     </row>
     <row r="197" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="B197" s="16" t="s">
+      <c r="B197" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C197" s="14" t="s">
+      <c r="C197" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="D197" s="30" t="s">
+      <c r="D197" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="E197" s="5"/>
+      <c r="E197" s="10"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="B198" s="18" t="s">
+      <c r="B198" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="C198" s="26" t="s">
+      <c r="C198" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D198" s="30" t="s">
+      <c r="D198" s="13" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B199" s="16" t="s">
+      <c r="B199" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="C199" s="11" t="s">
+      <c r="C199" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D199" s="30" t="s">
+      <c r="D199" s="13" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="B200" s="16" t="s">
+      <c r="B200" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="C200" s="11" t="s">
+      <c r="C200" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D200" s="30" t="s">
+      <c r="D200" s="13" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="B201" s="16" t="s">
+      <c r="B201" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="C201" s="11" t="s">
+      <c r="C201" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D201" s="30" t="s">
+      <c r="D201" s="13" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="A202" s="3" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="A203" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="B203" s="16" t="s">
+      <c r="B203" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C203" s="21" t="s">
+      <c r="C203" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="D203" s="30" t="s">
+      <c r="D203" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="E203" s="5"/>
+      <c r="E203" s="10"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="C204" s="21"/>
-      <c r="D204" s="30"/>
-      <c r="E204" s="5"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="13"/>
+      <c r="E204" s="10"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="A205" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="B205" s="16" t="s">
+      <c r="B205" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C205" s="21" t="s">
+      <c r="C205" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D205" s="30" t="s">
+      <c r="D205" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="E205" s="5"/>
+      <c r="E205" s="10"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="A206" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B206" s="16" t="s">
+      <c r="B206" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C206" s="21" t="s">
+      <c r="C206" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D206" s="30" t="s">
+      <c r="D206" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="E206" s="5"/>
+      <c r="E206" s="10"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="A207" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="B207" s="16" t="s">
+      <c r="B207" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C207" s="21" t="s">
+      <c r="C207" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D207" s="30" t="s">
+      <c r="D207" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="E207" s="5"/>
+      <c r="E207" s="10"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="A208" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B208" s="16" t="s">
+      <c r="B208" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C208" s="21" t="s">
+      <c r="C208" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="D208" s="30" t="s">
+      <c r="D208" s="13" t="s">
         <v>521</v>
       </c>
-      <c r="E208" s="5"/>
+      <c r="E208" s="10"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="A209" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B209" s="16" t="s">
+      <c r="B209" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C209" s="21" t="s">
+      <c r="C209" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="D209" s="30" t="s">
+      <c r="D209" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="E209" s="5"/>
-    </row>
-    <row r="210" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="E209" s="10"/>
+    </row>
+    <row r="210" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="B210" s="16" t="s">
+      <c r="B210" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C210" s="23" t="s">
+      <c r="C210" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="D210" s="30" t="s">
+      <c r="D210" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="E210" s="5"/>
+      <c r="E210" s="10"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="A211" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="B211" s="16" t="s">
+      <c r="B211" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C211" s="21" t="s">
+      <c r="C211" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D211" s="30" t="s">
+      <c r="D211" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="E211" s="5"/>
+      <c r="E211" s="10"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="A212" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B212" s="16" t="s">
+      <c r="B212" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C212" s="21" t="s">
+      <c r="C212" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D212" s="30" t="s">
+      <c r="D212" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="E212" s="5"/>
+      <c r="E212" s="10"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="B213" s="16" t="s">
+      <c r="B213" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C213" s="21" t="s">
+      <c r="C213" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D213" s="30" t="s">
+      <c r="D213" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="E213" s="5"/>
+      <c r="E213" s="10"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="A214" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="B214" s="16" t="s">
+      <c r="B214" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C214" s="21" t="s">
+      <c r="C214" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D214" s="30" t="s">
+      <c r="D214" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="E214" s="5"/>
+      <c r="E214" s="10"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="A215" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="B215" s="16" t="s">
+      <c r="B215" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C215" s="21" t="s">
+      <c r="C215" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D215" s="30" t="s">
+      <c r="D215" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E215" s="5"/>
+      <c r="E215" s="10"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="A216" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="B216" s="16" t="s">
+      <c r="B216" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C216" s="21" t="s">
+      <c r="C216" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D216" s="30" t="s">
+      <c r="D216" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="E216" s="5"/>
+      <c r="E216" s="10"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="A217" s="3" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="A218" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="B218" s="19" t="s">
+      <c r="B218" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="C218" s="21" t="s">
+      <c r="C218" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D218" s="30" t="s">
+      <c r="D218" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="E218" s="5"/>
+      <c r="E218" s="10"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="A219" s="3" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="A220" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="B220" s="16" t="s">
+      <c r="B220" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C220" s="21" t="s">
+      <c r="C220" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="D220" s="30" t="s">
+      <c r="D220" s="13" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="A221" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="B221" s="16" t="s">
+      <c r="B221" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C221" s="21" t="s">
+      <c r="C221" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D221" s="30" t="s">
+      <c r="D221" s="13" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="A222" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="B222" s="16" t="s">
+      <c r="B222" s="5" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+    <row r="223" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="B223" s="16" t="s">
+      <c r="B223" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C223" s="11" t="s">
+      <c r="C223" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="D223" s="34" t="s">
+      <c r="D223" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="E223" s="4" t="s">
+      <c r="E223" s="17" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="A224" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="B224" s="16" t="s">
+      <c r="B224" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C224" s="11" t="s">
+      <c r="C224" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="D224" s="30" t="s">
+      <c r="D224" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="E224" s="5"/>
+      <c r="E224" s="10"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="A225" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="B225" s="16" t="s">
+      <c r="B225" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C225" s="11" t="s">
+      <c r="C225" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="D225" s="30" t="s">
+      <c r="D225" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="E225" s="5"/>
+      <c r="E225" s="10"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="A226" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B226" s="16" t="s">
+      <c r="B226" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C226" s="11" t="s">
+      <c r="C226" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="D226" s="30" t="s">
+      <c r="D226" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="E226" s="5"/>
+      <c r="E226" s="10"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="A227" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="B227" s="16" t="s">
+      <c r="B227" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C227" s="11" t="s">
+      <c r="C227" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="D227" s="30" t="s">
+      <c r="D227" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="E227" s="5"/>
+      <c r="E227" s="10"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="A228" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="B228" s="16" t="s">
+      <c r="B228" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C228" s="11" t="s">
+      <c r="C228" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D228" s="30" t="s">
+      <c r="D228" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="E228" s="5"/>
+      <c r="E228" s="10"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="A229" s="3" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+    <row r="230" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="B230" s="16" t="s">
+      <c r="B230" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C230" s="12" t="s">
+      <c r="C230" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="D230" s="35" t="s">
+      <c r="D230" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E230" s="5"/>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="E230" s="10"/>
+    </row>
+    <row r="231" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="B231" s="16" t="s">
+      <c r="B231" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C231" s="12" t="s">
+      <c r="C231" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="D231" s="35" t="s">
+      <c r="D231" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E231" s="5"/>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="E231" s="10"/>
+    </row>
+    <row r="232" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="B232" s="16" t="s">
+      <c r="B232" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C232" s="12" t="s">
+      <c r="C232" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="D232" s="35" t="s">
+      <c r="D232" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E232" s="5"/>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="E232" s="10"/>
+    </row>
+    <row r="233" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="B233" s="16" t="s">
+      <c r="B233" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C233" s="12" t="s">
+      <c r="C233" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="D233" s="35" t="s">
+      <c r="D233" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E233" s="5"/>
+      <c r="E233" s="10"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+      <c r="A234" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="B234" s="16" t="s">
+      <c r="B234" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C234" s="11" t="s">
+      <c r="C234" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D234" s="35" t="s">
+      <c r="D234" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E234" s="5"/>
+      <c r="E234" s="10"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="A235" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B235" s="16" t="s">
+      <c r="B235" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C235" s="11" t="s">
+      <c r="C235" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="D235" s="35" t="s">
+      <c r="D235" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E235" s="5"/>
+      <c r="E235" s="10"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+      <c r="A236" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="B236" s="16" t="s">
+      <c r="B236" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C236" s="11" t="s">
+      <c r="C236" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D236" s="30" t="s">
+      <c r="D236" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="E236" s="5"/>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="E236" s="10"/>
+    </row>
+    <row r="237" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="B237" s="16" t="s">
+      <c r="B237" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C237" s="12" t="s">
+      <c r="C237" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="D237" s="30" t="s">
+      <c r="D237" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="E237" s="4" t="s">
+      <c r="E237" s="17" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+      <c r="A238" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="B238" s="17" t="s">
+      <c r="B238" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C238" s="28" t="s">
+      <c r="C238" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D238" s="31" t="s">
+      <c r="D238" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E238" s="1"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+      <c r="A239" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="B239" s="17" t="s">
+      <c r="B239" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C239" s="22" t="s">
+      <c r="C239" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D239" s="31" t="s">
+      <c r="D239" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E239" s="1"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+      <c r="A240" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B240" s="17" t="s">
+      <c r="B240" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C240" s="22" t="s">
+      <c r="C240" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D240" s="31" t="s">
+      <c r="D240" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E240" s="1"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+      <c r="A241" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B241" s="17" t="s">
+      <c r="B241" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C241" s="22" t="s">
+      <c r="C241" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D241" s="31" t="s">
+      <c r="D241" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E241" s="1"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+      <c r="A242" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="B242" s="17" t="s">
+      <c r="B242" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C242" s="22" t="s">
+      <c r="C242" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D242" s="31" t="s">
+      <c r="D242" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E242" s="1"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+      <c r="A243" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B243" s="17" t="s">
+      <c r="B243" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C243" s="22" t="s">
+      <c r="C243" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D243" s="31" t="s">
+      <c r="D243" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E243" s="1"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+      <c r="A244" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="B244" s="17" t="s">
+      <c r="B244" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C244" s="22" t="s">
+      <c r="C244" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D244" s="31" t="s">
+      <c r="D244" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E244" s="1"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="A245" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="B245" s="16" t="s">
+      <c r="B245" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C245" s="21" t="s">
+      <c r="C245" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D245" s="30" t="s">
+      <c r="D245" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="E245" s="5"/>
+      <c r="E245" s="10"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="A246" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="B246" s="16" t="s">
+      <c r="B246" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C246" s="21" t="s">
+      <c r="C246" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D246" s="30" t="s">
+      <c r="D246" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E246" s="5"/>
+      <c r="E246" s="10"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+      <c r="A247" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B247" s="16" t="s">
+      <c r="B247" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C247" s="21" t="s">
+      <c r="C247" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D247" s="30" t="s">
+      <c r="D247" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E247" s="5"/>
+      <c r="E247" s="10"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="A248" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="B248" s="16" t="s">
+      <c r="B248" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C248" s="21" t="s">
+      <c r="C248" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D248" s="30" t="s">
+      <c r="D248" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E248" s="5"/>
+      <c r="E248" s="10"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+      <c r="A249" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="B249" s="16" t="s">
+      <c r="B249" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C249" s="21" t="s">
+      <c r="C249" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D249" s="30" t="s">
+      <c r="D249" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E249" s="5"/>
+      <c r="E249" s="10"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+      <c r="A250" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="B250" s="16" t="s">
+      <c r="B250" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C250" s="21" t="s">
+      <c r="C250" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D250" s="30" t="s">
+      <c r="D250" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="E250" s="5"/>
+      <c r="E250" s="10"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="A251" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B251" s="16" t="s">
+      <c r="B251" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C251" s="21" t="s">
+      <c r="C251" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D251" s="30" t="s">
+      <c r="D251" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="E251" s="5"/>
+      <c r="E251" s="10"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+      <c r="A252" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="B252" s="16" t="s">
+      <c r="B252" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C252" s="21" t="s">
+      <c r="C252" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D252" s="30" t="s">
+      <c r="D252" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E252" s="5"/>
+      <c r="E252" s="10"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+      <c r="A253" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="B253" s="16" t="s">
+      <c r="B253" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C253" s="21" t="s">
+      <c r="C253" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D253" s="30" t="s">
+      <c r="D253" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="E253" s="5"/>
+      <c r="E253" s="10"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+      <c r="A254" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B254" s="16" t="s">
+      <c r="B254" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C254" s="21" t="s">
+      <c r="C254" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D254" s="30" t="s">
+      <c r="D254" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E254" s="5"/>
+      <c r="E254" s="10"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="A255" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="B255" s="16" t="s">
+      <c r="B255" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C255" s="21" t="s">
+      <c r="C255" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D255" s="30" t="s">
+      <c r="D255" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="E255" s="6"/>
+      <c r="E255" s="16"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="A256" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="B256" s="16" t="s">
+      <c r="B256" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C256" s="21" t="s">
+      <c r="C256" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D256" s="30" t="s">
+      <c r="D256" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E256" s="6"/>
+      <c r="E256" s="16"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="A257" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B257" s="16" t="s">
+      <c r="B257" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C257" s="21" t="s">
+      <c r="C257" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D257" s="30" t="s">
+      <c r="D257" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E257" s="5"/>
+      <c r="E257" s="10"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+      <c r="A258" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="B258" s="16" t="s">
+      <c r="B258" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C258" s="21" t="s">
+      <c r="C258" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D258" s="30" t="s">
+      <c r="D258" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E258" s="5"/>
+      <c r="E258" s="10"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
+      <c r="A259" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="B259" s="16" t="s">
+      <c r="B259" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C259" s="21" t="s">
+      <c r="C259" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D259" s="30" t="s">
+      <c r="D259" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="E259" s="5"/>
+      <c r="E259" s="10"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="A260" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="B260" s="16" t="s">
+      <c r="B260" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C260" s="21" t="s">
+      <c r="C260" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D260" s="30" t="s">
+      <c r="D260" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="E260" s="5"/>
+      <c r="E260" s="10"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="A261" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="B261" s="16" t="s">
+      <c r="B261" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C261" s="21" t="s">
+      <c r="C261" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D261" s="30" t="s">
+      <c r="D261" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E261" s="5"/>
+      <c r="E261" s="10"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="A262" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="B262" s="16" t="s">
+      <c r="B262" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C262" s="21" t="s">
+      <c r="C262" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D262" s="30" t="s">
+      <c r="D262" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="E262" s="5"/>
+      <c r="E262" s="10"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
+      <c r="A263" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="B263" s="16" t="s">
+      <c r="B263" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C263" s="21" t="s">
+      <c r="C263" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D263" s="30" t="s">
+      <c r="D263" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="E263" s="5"/>
+      <c r="E263" s="10"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+      <c r="A264" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="B264" s="16" t="s">
+      <c r="B264" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C264" s="21" t="s">
+      <c r="C264" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D264" s="30" t="s">
+      <c r="D264" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="E264" s="5"/>
+      <c r="E264" s="10"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="A265" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="B265" s="16" t="s">
+      <c r="B265" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C265" s="21" t="s">
+      <c r="C265" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D265" s="30" t="s">
+      <c r="D265" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="E265" s="5"/>
+      <c r="E265" s="10"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="A266" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="B266" s="16" t="s">
+      <c r="B266" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C266" s="21" t="s">
+      <c r="C266" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D266" s="30" t="s">
+      <c r="D266" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="E266" s="5"/>
+      <c r="E266" s="10"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
+      <c r="A267" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="B267" s="16" t="s">
+      <c r="B267" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C267" s="21" t="s">
+      <c r="C267" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D267" s="30" t="s">
+      <c r="D267" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="E267" s="5"/>
+      <c r="E267" s="10"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="A268" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B268" s="16" t="s">
+      <c r="B268" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C268" s="21" t="s">
+      <c r="C268" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D268" s="30" t="s">
+      <c r="D268" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="E268" s="5"/>
+      <c r="E268" s="10"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
+      <c r="A269" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="B269" s="16" t="s">
+      <c r="B269" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C269" s="21" t="s">
+      <c r="C269" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D269" s="30" t="s">
+      <c r="D269" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="E269" s="5"/>
+      <c r="E269" s="10"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
+      <c r="A270" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="B270" s="16" t="s">
+      <c r="B270" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C270" s="21" t="s">
+      <c r="C270" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D270" s="30" t="s">
+      <c r="D270" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="E270" s="4" t="s">
+      <c r="E270" s="17" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+      <c r="A271" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="B271" s="16" t="s">
+      <c r="B271" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C271" s="21" t="s">
+      <c r="C271" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D271" s="30" t="s">
+      <c r="D271" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="E271" s="5"/>
+      <c r="E271" s="10"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="B272" s="16" t="s">
+      <c r="B272" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C272" s="21" t="s">
+      <c r="C272" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D272" s="30" t="s">
+      <c r="D272" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="E272" s="5"/>
+      <c r="E272" s="10"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="A273" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="B273" s="16" t="s">
+      <c r="B273" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C273" s="21" t="s">
+      <c r="C273" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D273" s="30" t="s">
+      <c r="D273" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E273" s="5"/>
+      <c r="E273" s="10"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
+      <c r="A274" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="B274" s="16" t="s">
+      <c r="B274" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C274" s="21" t="s">
+      <c r="C274" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D274" s="30" t="s">
+      <c r="D274" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="E274" s="5"/>
+      <c r="E274" s="10"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="A275" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="B275" s="16" t="s">
+      <c r="B275" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C275" s="21" t="s">
+      <c r="C275" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D275" s="30" t="s">
+      <c r="D275" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E275" s="5"/>
+      <c r="E275" s="10"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+      <c r="A276" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="B276" s="16" t="s">
+      <c r="B276" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C276" s="21" t="s">
+      <c r="C276" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D276" s="30" t="s">
+      <c r="D276" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E276" s="5"/>
+      <c r="E276" s="10"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
+      <c r="A277" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="B277" s="16" t="s">
+      <c r="B277" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C277" s="21" t="s">
+      <c r="C277" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D277" s="30" t="s">
+      <c r="D277" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="E277" s="7"/>
+      <c r="E277" s="10"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="A278" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="B278" s="16" t="s">
+      <c r="B278" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C278" s="21" t="s">
+      <c r="C278" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D278" s="30" t="s">
+      <c r="D278" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="E278" s="5"/>
+      <c r="E278" s="10"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="A279" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="B279" s="16" t="s">
+      <c r="B279" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C279" s="21" t="s">
+      <c r="C279" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D279" s="30" t="s">
+      <c r="D279" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E279" s="5"/>
+      <c r="E279" s="10"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+      <c r="A280" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="B280" s="16" t="s">
+      <c r="B280" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C280" s="21" t="s">
+      <c r="C280" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D280" s="30" t="s">
+      <c r="D280" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="E280" s="5"/>
+      <c r="E280" s="10"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+      <c r="A281" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="B281" s="16" t="s">
+      <c r="B281" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C281" s="21" t="s">
+      <c r="C281" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D281" s="30" t="s">
+      <c r="D281" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="E281" s="5"/>
+      <c r="E281" s="10"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="A282" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="B282" s="16" t="s">
+      <c r="B282" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C282" s="21" t="s">
+      <c r="C282" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D282" s="30" t="s">
+      <c r="D282" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="E282" s="5"/>
+      <c r="E282" s="10"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="A283" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="B283" s="16" t="s">
+      <c r="B283" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C283" s="21" t="s">
+      <c r="C283" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D283" s="30" t="s">
+      <c r="D283" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E283" s="5"/>
+      <c r="E283" s="10"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="A284" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="B284" s="16" t="s">
+      <c r="B284" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C284" s="21" t="s">
+      <c r="C284" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D284" s="30" t="s">
+      <c r="D284" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E284" s="5"/>
+      <c r="E284" s="10"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
+      <c r="A285" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="B285" s="16" t="s">
+      <c r="B285" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C285" s="21" t="s">
+      <c r="C285" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D285" s="30" t="s">
+      <c r="D285" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="E285" s="5"/>
+      <c r="E285" s="10"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+      <c r="A286" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="B286" s="16" t="s">
+      <c r="B286" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C286" s="21" t="s">
+      <c r="C286" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D286" s="30" t="s">
+      <c r="D286" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E286" s="5"/>
+      <c r="E286" s="10"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
+      <c r="A287" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="B287" s="16" t="s">
+      <c r="B287" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C287" s="21" t="s">
+      <c r="C287" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D287" s="30" t="s">
+      <c r="D287" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="E287" s="5"/>
+      <c r="E287" s="10"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+      <c r="A288" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="B288" s="16" t="s">
+      <c r="B288" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C288" s="21" t="s">
+      <c r="C288" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D288" s="30" t="s">
+      <c r="D288" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E288" s="5"/>
+      <c r="E288" s="10"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
+      <c r="A289" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="B289" s="16" t="s">
+      <c r="B289" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C289" s="21" t="s">
+      <c r="C289" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D289" s="30" t="s">
+      <c r="D289" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="E289" s="5"/>
+      <c r="E289" s="10"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+      <c r="A290" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="B290" s="16" t="s">
+      <c r="B290" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C290" s="21" t="s">
+      <c r="C290" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D290" s="30" t="s">
+      <c r="D290" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E290" s="5"/>
+      <c r="E290" s="10"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
+      <c r="A291" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="B291" s="16" t="s">
+      <c r="B291" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C291" s="21" t="s">
+      <c r="C291" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D291" s="30" t="s">
+      <c r="D291" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E291" s="5"/>
+      <c r="E291" s="10"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
+      <c r="A292" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="B292" s="16" t="s">
+      <c r="B292" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C292" s="21" t="s">
+      <c r="C292" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D292" s="30" t="s">
+      <c r="D292" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E292" s="5"/>
+      <c r="E292" s="10"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
+      <c r="A293" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="B293" s="16" t="s">
+      <c r="B293" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C293" s="21" t="s">
+      <c r="C293" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D293" s="30" t="s">
+      <c r="D293" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E293" s="5"/>
+      <c r="E293" s="10"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
+      <c r="A294" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="B294" s="16" t="s">
+      <c r="B294" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C294" s="21" t="s">
+      <c r="C294" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D294" s="30" t="s">
+      <c r="D294" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="E294" s="5"/>
+      <c r="E294" s="10"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
+      <c r="A295" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="B295" s="16" t="s">
+      <c r="B295" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C295" s="21" t="s">
+      <c r="C295" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="D295" s="30" t="s">
+      <c r="D295" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E295" s="5"/>
+      <c r="E295" s="10"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
+      <c r="A296" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="B296" s="16" t="s">
+      <c r="B296" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C296" s="21" t="s">
+      <c r="C296" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D296" s="30" t="s">
+      <c r="D296" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="E296" s="5"/>
+      <c r="E296" s="10"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="A297" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="B297" s="16" t="s">
+      <c r="B297" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C297" s="21" t="s">
+      <c r="C297" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D297" s="30" t="s">
+      <c r="D297" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="E297" s="4" t="s">
+      <c r="E297" s="17" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
+      <c r="A298" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="B298" s="16" t="s">
+      <c r="B298" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C298" s="11" t="s">
+      <c r="C298" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D298" s="30" t="s">
+      <c r="D298" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E298" s="5"/>
-    </row>
-    <row r="299" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
+      <c r="E298" s="10"/>
+    </row>
+    <row r="299" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="B299" s="16" t="s">
+      <c r="B299" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C299" s="23" t="s">
+      <c r="C299" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="D299" s="30" t="s">
+      <c r="D299" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E299" s="5"/>
+      <c r="E299" s="10"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="A300" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="B300" s="16" t="s">
+      <c r="B300" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C300" s="21" t="s">
+      <c r="C300" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D300" s="30" t="s">
+      <c r="D300" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="E300" s="5"/>
-    </row>
-    <row r="301" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="E300" s="10"/>
+    </row>
+    <row r="301" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="B301" s="16" t="s">
+      <c r="B301" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C301" s="12" t="s">
+      <c r="C301" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D301" s="30" t="s">
+      <c r="D301" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E301" s="4" t="s">
+      <c r="E301" s="17" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
+      <c r="A302" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="B302" s="16" t="s">
+      <c r="B302" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C302" s="21" t="s">
+      <c r="C302" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D302" s="32"/>
-      <c r="E302" s="5"/>
+      <c r="D302" s="10"/>
+      <c r="E302" s="10"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+      <c r="A303" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="B303" s="16" t="s">
+      <c r="B303" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C303" s="21" t="s">
+      <c r="C303" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D303" s="30" t="s">
+      <c r="D303" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="E303" s="5"/>
+      <c r="E303" s="10"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
+      <c r="A304" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="B304" s="16" t="s">
+      <c r="B304" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C304" s="21" t="s">
+      <c r="C304" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="D304" s="30" t="s">
+      <c r="D304" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="E304" s="5"/>
+      <c r="E304" s="10"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
+      <c r="A305" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="B305" s="16" t="s">
+      <c r="B305" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C305" s="21" t="s">
+      <c r="C305" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D305" s="30" t="s">
+      <c r="D305" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E305" s="8" t="s">
+      <c r="E305" s="17" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+      <c r="A306" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="B306" s="16" t="s">
+      <c r="B306" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C306" s="21" t="s">
+      <c r="C306" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D306" s="30" t="s">
+      <c r="D306" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E306" s="5"/>
+      <c r="E306" s="10"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="A307" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="B307" s="16" t="s">
+      <c r="B307" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C307" s="21" t="s">
+      <c r="C307" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D307" s="30" t="s">
+      <c r="D307" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="E307" s="5"/>
+      <c r="E307" s="10"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="A308" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="B308" s="16" t="s">
+      <c r="B308" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C308" s="21" t="s">
+      <c r="C308" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D308" s="30" t="s">
+      <c r="D308" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="E308" s="5"/>
+      <c r="E308" s="10"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
+      <c r="A309" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="B309" s="16" t="s">
+      <c r="B309" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C309" s="21" t="s">
+      <c r="C309" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D309" s="30" t="s">
+      <c r="D309" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E309" s="5"/>
+      <c r="E309" s="10"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="A310" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="B310" s="16" t="s">
+      <c r="B310" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C310" s="21" t="s">
+      <c r="C310" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D310" s="30" t="s">
+      <c r="D310" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="E310" s="5"/>
+      <c r="E310" s="10"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="A311" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B311" s="16" t="s">
+      <c r="B311" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C311" s="21" t="s">
+      <c r="C311" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D311" s="30" t="s">
+      <c r="D311" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="E311" s="5"/>
+      <c r="E311" s="10"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
+      <c r="A312" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="B312" s="16" t="s">
+      <c r="B312" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C312" s="21" t="s">
+      <c r="C312" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D312" s="30" t="s">
+      <c r="D312" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E312" s="5"/>
+      <c r="E312" s="10"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="A313" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="B313" s="16" t="s">
+      <c r="B313" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C313" s="24" t="s">
+      <c r="C313" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D313" s="30" t="s">
+      <c r="D313" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="E313" s="5"/>
+      <c r="E313" s="10"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="A314" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="B314" s="16" t="s">
+      <c r="B314" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C314" s="24" t="s">
+      <c r="C314" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D314" s="30" t="s">
+      <c r="D314" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E314" s="5"/>
+      <c r="E314" s="10"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
+      <c r="A315" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="B315" s="16" t="s">
+      <c r="B315" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C315" s="24" t="s">
+      <c r="C315" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D315" s="30" t="s">
+      <c r="D315" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="E315" s="5"/>
+      <c r="E315" s="10"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
+      <c r="A316" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="B316" s="16" t="s">
+      <c r="B316" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C316" s="24" t="s">
+      <c r="C316" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D316" s="30" t="s">
+      <c r="D316" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="E316" s="5"/>
+      <c r="E316" s="10"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+      <c r="A317" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="B317" s="16" t="s">
+      <c r="B317" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C317" s="24" t="s">
+      <c r="C317" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D317" s="30" t="s">
+      <c r="D317" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E317" s="5"/>
+      <c r="E317" s="10"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
+      <c r="A318" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="B318" s="16" t="s">
+      <c r="B318" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C318" s="21" t="s">
+      <c r="C318" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D318" s="30" t="s">
+      <c r="D318" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="E318" s="5"/>
+      <c r="E318" s="10"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
+      <c r="A319" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="B319" s="16" t="s">
+      <c r="B319" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C319" s="24" t="s">
+      <c r="C319" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D319" s="30" t="s">
+      <c r="D319" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="E319" s="5"/>
+      <c r="E319" s="10"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="A320" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="B320" s="16" t="s">
+      <c r="B320" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C320" s="22" t="s">
+      <c r="C320" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D320" s="31" t="s">
+      <c r="D320" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E320" s="2"/>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="B321" s="16" t="s">
+      <c r="B321" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C321" s="22" t="s">
+      <c r="C321" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D321" s="31" t="s">
+      <c r="D321" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E321" s="2"/>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D322" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D323" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D324" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="B326" s="8"/>
+      <c r="C326" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D327" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="B328" s="8"/>
+      <c r="C328" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D328" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="B329" s="8"/>
+      <c r="C329" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D329" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="B330" s="8"/>
+      <c r="C330" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D330" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D331" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D332" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D333" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D334" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D335" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D336" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D337" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D338" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D339" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D340" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D341" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D342" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D343" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D344" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D345" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D346" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D347" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D348" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D349" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D350" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D351" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D352" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D353" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D354" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D355" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D356" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D357" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B358" s="2"/>
+      <c r="C358" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="D358" s="14" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="D359" s="14" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D360" s="14" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B361" s="2"/>
+      <c r="C361" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="D361" s="14" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B362" s="2"/>
+      <c r="C362" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B363" s="2"/>
+      <c r="C363" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B366" s="2"/>
+      <c r="C366" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B369" s="2"/>
+      <c r="C369" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B370" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B371" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B372" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B373" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B374" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B375" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B376" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B377" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B378" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B380" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B381" s="2"/>
+      <c r="C381" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>965</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8385,8 +9481,45 @@
     <hyperlink ref="D319" r:id="rId325"/>
     <hyperlink ref="D320" r:id="rId326"/>
     <hyperlink ref="D321" r:id="rId327"/>
+    <hyperlink ref="D322" r:id="rId328"/>
+    <hyperlink ref="D323" r:id="rId329"/>
+    <hyperlink ref="D324" r:id="rId330"/>
+    <hyperlink ref="D325" r:id="rId331"/>
+    <hyperlink ref="D326" r:id="rId332"/>
+    <hyperlink ref="D327" r:id="rId333"/>
+    <hyperlink ref="D328" r:id="rId334"/>
+    <hyperlink ref="D329" r:id="rId335"/>
+    <hyperlink ref="D330" r:id="rId336"/>
+    <hyperlink ref="D331" r:id="rId337"/>
+    <hyperlink ref="D332" r:id="rId338"/>
+    <hyperlink ref="D333" r:id="rId339"/>
+    <hyperlink ref="D334" r:id="rId340"/>
+    <hyperlink ref="D335" r:id="rId341"/>
+    <hyperlink ref="D336" r:id="rId342"/>
+    <hyperlink ref="D337" r:id="rId343"/>
+    <hyperlink ref="D338" r:id="rId344"/>
+    <hyperlink ref="D339" r:id="rId345"/>
+    <hyperlink ref="D340" r:id="rId346"/>
+    <hyperlink ref="D341" r:id="rId347"/>
+    <hyperlink ref="D342" r:id="rId348"/>
+    <hyperlink ref="D343" r:id="rId349"/>
+    <hyperlink ref="D344" r:id="rId350"/>
+    <hyperlink ref="D345" r:id="rId351"/>
+    <hyperlink ref="D348" r:id="rId352"/>
+    <hyperlink ref="D349" r:id="rId353"/>
+    <hyperlink ref="D350" r:id="rId354"/>
+    <hyperlink ref="D351" r:id="rId355"/>
+    <hyperlink ref="D352" r:id="rId356"/>
+    <hyperlink ref="D353" r:id="rId357"/>
+    <hyperlink ref="D354" r:id="rId358"/>
+    <hyperlink ref="D355" r:id="rId359"/>
+    <hyperlink ref="D356" r:id="rId360"/>
+    <hyperlink ref="D357" r:id="rId361"/>
+    <hyperlink ref="D358" r:id="rId362"/>
+    <hyperlink ref="D360" r:id="rId363"/>
+    <hyperlink ref="D361" r:id="rId364"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId328"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId365"/>
 </worksheet>
 </file>
--- a/data/TDS.xlsx
+++ b/data/TDS.xlsx
@@ -6521,7 +6521,7 @@
       </c>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>768</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>801</v>
       </c>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="E230" s="10"/>
     </row>
-    <row r="231" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>802</v>
       </c>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="E231" s="10"/>
     </row>
-    <row r="232" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>803</v>
       </c>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="E232" s="10"/>
     </row>
-    <row r="233" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>804</v>
       </c>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="E236" s="10"/>
     </row>
-    <row r="237" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>808</v>
       </c>
@@ -8319,7 +8319,7 @@
       <c r="C320" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D320" s="14" t="s">
+      <c r="D320" s="19" t="s">
         <v>42</v>
       </c>
     </row>

--- a/data/TDS.xlsx
+++ b/data/TDS.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="1023">
   <si>
     <t>https://www.hindcon.com/wp-content/uploads/2026/09/HIND-ELASTOFLEX-7492.pdf</t>
   </si>
@@ -2345,13 +2345,7 @@
     <t>HC200</t>
   </si>
   <si>
-    <t>HC201</t>
-  </si>
-  <si>
     <t>HC202</t>
-  </si>
-  <si>
-    <t>HC203</t>
   </si>
   <si>
     <t>HC204</t>
@@ -3563,7 +3557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E379"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3578,16 +3572,16 @@
         <v>572</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>891</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>892</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>893</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="E1" s="23" t="s">
         <v>894</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>895</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6394,7 +6388,7 @@
         <v>564</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D188" s="13" t="s">
         <v>492</v>
@@ -6409,7 +6403,7 @@
         <v>564</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D189" s="13" t="s">
         <v>493</v>
@@ -6439,7 +6433,7 @@
         <v>564</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D191" s="13" t="s">
         <v>496</v>
@@ -6596,19 +6590,29 @@
       <c r="A202" s="3" t="s">
         <v>773</v>
       </c>
+      <c r="B202" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="E202" s="10"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>774</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>516</v>
+        <v>247</v>
       </c>
       <c r="D203" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E203" s="10"/>
     </row>
@@ -6616,8 +6620,15 @@
       <c r="A204" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="C204" s="4"/>
-      <c r="D204" s="13"/>
+      <c r="B204" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>485</v>
+      </c>
       <c r="E204" s="10"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -6628,10 +6639,10 @@
         <v>568</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="D205" s="13" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E205" s="10"/>
     </row>
@@ -6643,10 +6654,10 @@
         <v>568</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>484</v>
+        <v>520</v>
       </c>
       <c r="D206" s="13" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E206" s="10"/>
     </row>
@@ -6658,25 +6669,25 @@
         <v>568</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>292</v>
+        <v>522</v>
       </c>
       <c r="D207" s="13" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E207" s="10"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>779</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C208" s="4" t="s">
-        <v>520</v>
+      <c r="C208" s="11" t="s">
+        <v>524</v>
       </c>
       <c r="D208" s="13" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E208" s="10"/>
     </row>
@@ -6688,25 +6699,25 @@
         <v>568</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>522</v>
+        <v>199</v>
       </c>
       <c r="D209" s="13" t="s">
-        <v>523</v>
+        <v>200</v>
       </c>
       <c r="E209" s="10"/>
     </row>
-    <row r="210" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>781</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C210" s="11" t="s">
-        <v>524</v>
+      <c r="C210" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="D210" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E210" s="10"/>
     </row>
@@ -6718,10 +6729,10 @@
         <v>568</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="D211" s="13" t="s">
-        <v>200</v>
+        <v>527</v>
       </c>
       <c r="E211" s="10"/>
     </row>
@@ -6733,10 +6744,10 @@
         <v>568</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>324</v>
+        <v>450</v>
       </c>
       <c r="D212" s="13" t="s">
-        <v>526</v>
+        <v>451</v>
       </c>
       <c r="E212" s="10"/>
     </row>
@@ -6748,10 +6759,10 @@
         <v>568</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D213" s="13" t="s">
-        <v>527</v>
+        <v>282</v>
       </c>
       <c r="E213" s="10"/>
     </row>
@@ -6763,10 +6774,10 @@
         <v>568</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>450</v>
+        <v>322</v>
       </c>
       <c r="D214" s="13" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="E214" s="10"/>
     </row>
@@ -6774,29 +6785,19 @@
       <c r="A215" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="B215" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D215" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E215" s="10"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="B216" s="5" t="s">
-        <v>568</v>
+      <c r="B216" s="7" t="s">
+        <v>529</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>322</v>
+        <v>530</v>
       </c>
       <c r="D216" s="13" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E216" s="10"/>
     </row>
@@ -6809,21 +6810,29 @@
       <c r="A218" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="B218" s="7" t="s">
-        <v>529</v>
+      <c r="B218" s="5" t="s">
+        <v>569</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D218" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="E218" s="10"/>
+        <v>533</v>
+      </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>790</v>
       </c>
+      <c r="B219" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D219" s="13" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
@@ -6832,25 +6841,22 @@
       <c r="B220" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C220" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="D220" s="13" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>792</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="D221" s="13" t="s">
-        <v>535</v>
+        <v>536</v>
+      </c>
+      <c r="D221" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="E221" s="17" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6858,10 +6864,17 @@
         <v>793</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D222" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="E222" s="10"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>794</v>
       </c>
@@ -6869,14 +6882,12 @@
         <v>570</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="D223" s="15" t="s">
-        <v>537</v>
-      </c>
-      <c r="E223" s="17" t="s">
-        <v>538</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="D223" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="E223" s="10"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
@@ -6886,10 +6897,10 @@
         <v>570</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E224" s="10"/>
     </row>
@@ -6901,10 +6912,10 @@
         <v>570</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D225" s="13" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E225" s="10"/>
     </row>
@@ -6916,10 +6927,10 @@
         <v>570</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D226" s="13" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E226" s="10"/>
     </row>
@@ -6927,29 +6938,19 @@
       <c r="A227" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="B227" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="D227" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="E227" s="10"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>799</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="D228" s="13" t="s">
-        <v>548</v>
+        <v>571</v>
+      </c>
+      <c r="C228" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="D228" s="16" t="s">
+        <v>550</v>
       </c>
       <c r="E228" s="10"/>
     </row>
@@ -6957,6 +6958,16 @@
       <c r="A229" s="3" t="s">
         <v>800</v>
       </c>
+      <c r="B229" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="D229" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E229" s="10"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
@@ -6966,7 +6977,7 @@
         <v>571</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D230" s="16" t="s">
         <v>550</v>
@@ -6981,7 +6992,7 @@
         <v>571</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D231" s="16" t="s">
         <v>550</v>
@@ -6995,8 +7006,8 @@
       <c r="B232" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C232" s="11" t="s">
-        <v>552</v>
+      <c r="C232" s="4" t="s">
+        <v>554</v>
       </c>
       <c r="D232" s="16" t="s">
         <v>550</v>
@@ -7010,8 +7021,8 @@
       <c r="B233" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C233" s="11" t="s">
-        <v>553</v>
+      <c r="C233" s="4" t="s">
+        <v>555</v>
       </c>
       <c r="D233" s="16" t="s">
         <v>550</v>
@@ -7026,10 +7037,10 @@
         <v>571</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="D234" s="16" t="s">
-        <v>550</v>
+        <v>556</v>
+      </c>
+      <c r="D234" s="13" t="s">
+        <v>557</v>
       </c>
       <c r="E234" s="10"/>
     </row>
@@ -7040,44 +7051,42 @@
       <c r="B235" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C235" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="D235" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="E235" s="10"/>
+      <c r="C235" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="D235" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="E235" s="17" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>807</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="D236" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="E236" s="10"/>
+        <v>66</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D236" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>808</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="C237" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D237" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="E237" s="17" t="s">
-        <v>560</v>
+        <v>66</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -7087,11 +7096,11 @@
       <c r="B238" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C238" s="12" t="s">
-        <v>65</v>
+      <c r="C238" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -7102,10 +7111,10 @@
         <v>66</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -7116,10 +7125,10 @@
         <v>66</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D240" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -7130,10 +7139,10 @@
         <v>66</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -7144,10 +7153,10 @@
         <v>66</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -7155,28 +7164,30 @@
         <v>814</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D243" s="14" t="s">
-        <v>76</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D243" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E243" s="10"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>815</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D244" s="14" t="s">
-        <v>78</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D244" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E244" s="10"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
@@ -7186,10 +7197,10 @@
         <v>40</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D245" s="13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E245" s="10"/>
     </row>
@@ -7201,10 +7212,10 @@
         <v>40</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D246" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E246" s="10"/>
     </row>
@@ -7216,10 +7227,10 @@
         <v>40</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D247" s="13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E247" s="10"/>
     </row>
@@ -7231,10 +7242,10 @@
         <v>40</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E248" s="10"/>
     </row>
@@ -7246,10 +7257,10 @@
         <v>40</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D249" s="13" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E249" s="10"/>
     </row>
@@ -7261,10 +7272,10 @@
         <v>40</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D250" s="13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E250" s="10"/>
     </row>
@@ -7276,10 +7287,10 @@
         <v>40</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D251" s="13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E251" s="10"/>
     </row>
@@ -7291,10 +7302,10 @@
         <v>40</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D252" s="13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E252" s="10"/>
     </row>
@@ -7306,12 +7317,12 @@
         <v>40</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="D253" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E253" s="10"/>
+        <v>178</v>
+      </c>
+      <c r="E253" s="16"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
@@ -7321,12 +7332,12 @@
         <v>40</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D254" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E254" s="10"/>
+        <v>180</v>
+      </c>
+      <c r="E254" s="16"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
@@ -7336,12 +7347,12 @@
         <v>40</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E255" s="16"/>
+        <v>182</v>
+      </c>
+      <c r="E255" s="10"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
@@ -7351,12 +7362,12 @@
         <v>40</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D256" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E256" s="16"/>
+        <v>184</v>
+      </c>
+      <c r="E256" s="10"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
@@ -7366,10 +7377,10 @@
         <v>40</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D257" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E257" s="10"/>
     </row>
@@ -7381,10 +7392,10 @@
         <v>40</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D258" s="13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E258" s="10"/>
     </row>
@@ -7396,10 +7407,10 @@
         <v>40</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E259" s="10"/>
     </row>
@@ -7411,10 +7422,10 @@
         <v>40</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D260" s="13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E260" s="10"/>
     </row>
@@ -7426,10 +7437,10 @@
         <v>40</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E261" s="10"/>
     </row>
@@ -7441,10 +7452,10 @@
         <v>40</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D262" s="13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E262" s="10"/>
     </row>
@@ -7456,10 +7467,10 @@
         <v>40</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E263" s="10"/>
     </row>
@@ -7471,10 +7482,10 @@
         <v>40</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D264" s="13" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E264" s="10"/>
     </row>
@@ -7486,10 +7497,10 @@
         <v>40</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E265" s="10"/>
     </row>
@@ -7501,10 +7512,10 @@
         <v>40</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D266" s="13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E266" s="10"/>
     </row>
@@ -7516,10 +7527,10 @@
         <v>40</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E267" s="10"/>
     </row>
@@ -7531,12 +7542,14 @@
         <v>40</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D268" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="E268" s="10"/>
+        <v>208</v>
+      </c>
+      <c r="E268" s="17" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
@@ -7546,10 +7559,10 @@
         <v>40</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E269" s="10"/>
     </row>
@@ -7561,14 +7574,12 @@
         <v>40</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="D270" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E270" s="17" t="s">
-        <v>209</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="E270" s="10"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
@@ -7578,10 +7589,10 @@
         <v>40</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E271" s="10"/>
     </row>
@@ -7593,10 +7604,10 @@
         <v>40</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="D272" s="13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E272" s="10"/>
     </row>
@@ -7608,10 +7619,10 @@
         <v>40</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E273" s="10"/>
     </row>
@@ -7623,10 +7634,10 @@
         <v>40</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D274" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E274" s="10"/>
     </row>
@@ -7638,10 +7649,10 @@
         <v>40</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E275" s="10"/>
     </row>
@@ -7653,10 +7664,10 @@
         <v>40</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D276" s="13" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E276" s="10"/>
     </row>
@@ -7668,10 +7679,10 @@
         <v>40</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E277" s="10"/>
     </row>
@@ -7683,10 +7694,10 @@
         <v>40</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D278" s="13" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E278" s="10"/>
     </row>
@@ -7698,10 +7709,10 @@
         <v>40</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D279" s="13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E279" s="10"/>
     </row>
@@ -7713,10 +7724,10 @@
         <v>40</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D280" s="13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E280" s="10"/>
     </row>
@@ -7728,10 +7739,10 @@
         <v>40</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D281" s="13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E281" s="10"/>
     </row>
@@ -7743,10 +7754,10 @@
         <v>40</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D282" s="13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E282" s="10"/>
     </row>
@@ -7758,10 +7769,10 @@
         <v>40</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E283" s="10"/>
     </row>
@@ -7773,10 +7784,10 @@
         <v>40</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D284" s="13" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E284" s="10"/>
     </row>
@@ -7788,10 +7799,10 @@
         <v>40</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E285" s="10"/>
     </row>
@@ -7803,10 +7814,10 @@
         <v>40</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E286" s="10"/>
     </row>
@@ -7818,10 +7829,10 @@
         <v>40</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E287" s="10"/>
     </row>
@@ -7833,10 +7844,10 @@
         <v>40</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D288" s="13" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E288" s="10"/>
     </row>
@@ -7848,10 +7859,10 @@
         <v>40</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E289" s="10"/>
     </row>
@@ -7863,10 +7874,10 @@
         <v>40</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E290" s="10"/>
     </row>
@@ -7878,10 +7889,10 @@
         <v>40</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E291" s="10"/>
     </row>
@@ -7893,10 +7904,10 @@
         <v>40</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D292" s="13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E292" s="10"/>
     </row>
@@ -7908,10 +7919,10 @@
         <v>40</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E293" s="10"/>
     </row>
@@ -7923,10 +7934,10 @@
         <v>40</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D294" s="13" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E294" s="10"/>
     </row>
@@ -7938,12 +7949,14 @@
         <v>40</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E295" s="10"/>
+        <v>262</v>
+      </c>
+      <c r="E295" s="17" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
@@ -7953,29 +7966,27 @@
         <v>40</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D296" s="13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E296" s="10"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>868</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C297" s="4" t="s">
-        <v>261</v>
+      <c r="C297" s="11" t="s">
+        <v>266</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E297" s="17" t="s">
-        <v>263</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="E297" s="10"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
@@ -7985,10 +7996,10 @@
         <v>40</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D298" s="13" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E298" s="10"/>
     </row>
@@ -8000,12 +8011,14 @@
         <v>40</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="E299" s="10"/>
+        <v>271</v>
+      </c>
+      <c r="E299" s="17" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
@@ -8015,29 +8028,25 @@
         <v>40</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D300" s="13" t="s">
-        <v>269</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="D300" s="10"/>
       <c r="E300" s="10"/>
     </row>
-    <row r="301" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>872</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C301" s="11" t="s">
-        <v>270</v>
+      <c r="C301" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="E301" s="17" t="s">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="E301" s="10"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
@@ -8047,9 +8056,11 @@
         <v>40</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D302" s="10"/>
+        <v>276</v>
+      </c>
+      <c r="D302" s="13" t="s">
+        <v>277</v>
+      </c>
       <c r="E302" s="10"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -8060,12 +8071,14 @@
         <v>40</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E303" s="10"/>
+        <v>279</v>
+      </c>
+      <c r="E303" s="17" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
@@ -8075,10 +8088,10 @@
         <v>40</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E304" s="10"/>
     </row>
@@ -8090,14 +8103,12 @@
         <v>40</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D305" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E305" s="17" t="s">
-        <v>280</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="E305" s="10"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
@@ -8107,10 +8118,10 @@
         <v>40</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D306" s="13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E306" s="10"/>
     </row>
@@ -8122,10 +8133,10 @@
         <v>40</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D307" s="13" t="s">
-        <v>284</v>
+        <v>48</v>
       </c>
       <c r="E307" s="10"/>
     </row>
@@ -8137,10 +8148,10 @@
         <v>40</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E308" s="10"/>
     </row>
@@ -8152,10 +8163,10 @@
         <v>40</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>48</v>
+        <v>291</v>
       </c>
       <c r="E309" s="10"/>
     </row>
@@ -8167,10 +8178,10 @@
         <v>40</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D310" s="13" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E310" s="10"/>
     </row>
@@ -8182,10 +8193,10 @@
         <v>40</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D311" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E311" s="10"/>
     </row>
@@ -8197,10 +8208,10 @@
         <v>40</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D312" s="13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E312" s="10"/>
     </row>
@@ -8212,10 +8223,10 @@
         <v>40</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D313" s="13" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E313" s="10"/>
     </row>
@@ -8227,10 +8238,10 @@
         <v>40</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D314" s="13" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E314" s="10"/>
     </row>
@@ -8242,10 +8253,10 @@
         <v>40</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D315" s="13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E315" s="10"/>
     </row>
@@ -8257,10 +8268,10 @@
         <v>40</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D316" s="13" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E316" s="10"/>
     </row>
@@ -8272,10 +8283,10 @@
         <v>40</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="D317" s="13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E317" s="10"/>
     </row>
@@ -8286,13 +8297,12 @@
       <c r="B318" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C318" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D318" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="E318" s="10"/>
+      <c r="C318" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D318" s="19" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
@@ -8301,40 +8311,39 @@
       <c r="B319" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C319" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D319" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="E319" s="10"/>
+      <c r="C319" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D319" s="14" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>40</v>
+        <v>964</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>898</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D320" s="19" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="D320" s="14" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="B321" s="5" t="s">
-        <v>40</v>
+        <v>965</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>898</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D321" s="14" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -8342,13 +8351,13 @@
         <v>966</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D322" s="14" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -8356,27 +8365,25 @@
         <v>967</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D323" s="14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="B324" s="8" t="s">
-        <v>901</v>
-      </c>
+      <c r="B324" s="8"/>
       <c r="C324" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D324" s="14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -8387,10 +8394,10 @@
         <v>900</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D325" s="14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -8399,24 +8406,22 @@
       </c>
       <c r="B326" s="8"/>
       <c r="C326" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D326" s="14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>971</v>
       </c>
-      <c r="B327" s="8" t="s">
-        <v>902</v>
-      </c>
+      <c r="B327" s="8"/>
       <c r="C327" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D327" s="14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -8425,34 +8430,38 @@
       </c>
       <c r="B328" s="8"/>
       <c r="C328" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D328" s="14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="B329" s="8"/>
+      <c r="B329" s="8" t="s">
+        <v>901</v>
+      </c>
       <c r="C329" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D329" s="14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="B330" s="8"/>
+      <c r="B330" s="8" t="s">
+        <v>902</v>
+      </c>
       <c r="C330" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D330" s="14" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -8460,13 +8469,13 @@
         <v>975</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D331" s="14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -8474,13 +8483,13 @@
         <v>976</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D332" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -8488,13 +8497,13 @@
         <v>977</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D333" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -8502,13 +8511,13 @@
         <v>978</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D334" s="14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -8519,10 +8528,10 @@
         <v>904</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D335" s="14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -8533,10 +8542,10 @@
         <v>905</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D336" s="14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -8547,10 +8556,10 @@
         <v>906</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D337" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -8561,38 +8570,38 @@
         <v>907</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D338" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="B339" s="8" t="s">
-        <v>908</v>
+      <c r="B339" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D339" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B340" s="8" t="s">
-        <v>909</v>
+      <c r="B340" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D340" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -8600,13 +8609,13 @@
         <v>985</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D341" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -8614,13 +8623,13 @@
         <v>986</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D342" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -8631,10 +8640,10 @@
         <v>45</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D343" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -8645,10 +8654,10 @@
         <v>45</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D344" s="14" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -8659,10 +8668,10 @@
         <v>45</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D345" s="14" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -8673,38 +8682,38 @@
         <v>45</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D346" s="14" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="B347" s="5" t="s">
-        <v>45</v>
+      <c r="B347" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D347" s="14" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="B348" s="5" t="s">
-        <v>45</v>
+      <c r="B348" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D348" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -8712,41 +8721,41 @@
         <v>993</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D349" s="14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="B350" s="8" t="s">
-        <v>57</v>
+      <c r="B350" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D350" s="14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="B351" s="8" t="s">
-        <v>66</v>
+      <c r="B351" s="2" t="s">
+        <v>908</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D351" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -8754,13 +8763,13 @@
         <v>996</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>67</v>
+        <v>909</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D352" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -8771,10 +8780,10 @@
         <v>910</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D353" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -8782,13 +8791,13 @@
         <v>998</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D354" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -8796,81 +8805,77 @@
         <v>999</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D355" s="14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>1000</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="2"/>
+      <c r="C356" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="D356" s="14" t="s">
         <v>912</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D356" s="14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="B357" s="2" t="s">
-        <v>912</v>
+      <c r="B357" s="8" t="s">
+        <v>904</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>77</v>
+        <v>913</v>
       </c>
       <c r="D357" s="14" t="s">
-        <v>78</v>
+        <v>914</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="B358" s="2"/>
+      <c r="B358" s="8" t="s">
+        <v>904</v>
+      </c>
       <c r="C358" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D358" s="14" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>1003</v>
       </c>
-      <c r="B359" s="8" t="s">
-        <v>906</v>
-      </c>
+      <c r="B359" s="2"/>
       <c r="C359" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D359" s="14" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="B360" s="8" t="s">
-        <v>906</v>
-      </c>
+      <c r="B360" s="2"/>
       <c r="C360" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="D360" s="14" t="s">
-        <v>918</v>
+        <v>919</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -8879,48 +8884,50 @@
       </c>
       <c r="B361" s="2"/>
       <c r="C361" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="D361" s="14" t="s">
-        <v>920</v>
+        <v>921</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="B362" s="2"/>
+      <c r="B362" s="2" t="s">
+        <v>923</v>
+      </c>
       <c r="C362" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="B363" s="2"/>
+      <c r="B363" s="2" t="s">
+        <v>926</v>
+      </c>
       <c r="C363" s="1" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="B364" s="2" t="s">
-        <v>925</v>
-      </c>
+      <c r="B364" s="2"/>
       <c r="C364" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -8928,65 +8935,67 @@
         <v>1009</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="B366" s="2"/>
+      <c r="B366" s="2" t="s">
+        <v>934</v>
+      </c>
       <c r="C366" s="1" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="B367" s="2" t="s">
-        <v>933</v>
-      </c>
+      <c r="B367" s="2"/>
       <c r="C367" s="1" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="B368" s="2" t="s">
-        <v>936</v>
+      <c r="B368" s="8" t="s">
+        <v>904</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="B369" s="2"/>
+      <c r="B369" s="8" t="s">
+        <v>904</v>
+      </c>
       <c r="C369" s="1" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -8994,13 +9003,13 @@
         <v>1014</v>
       </c>
       <c r="B370" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -9008,13 +9017,13 @@
         <v>1015</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -9022,13 +9031,13 @@
         <v>1016</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -9036,13 +9045,13 @@
         <v>1017</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -9050,13 +9059,13 @@
         <v>1018</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -9064,41 +9073,41 @@
         <v>1019</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="B376" s="8" t="s">
-        <v>906</v>
+      <c r="B376" s="9" t="s">
+        <v>907</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>1021</v>
       </c>
-      <c r="B377" s="8" t="s">
-        <v>906</v>
+      <c r="B377" s="9" t="s">
+        <v>957</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -9106,50 +9115,22 @@
         <v>1022</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>909</v>
+        <v>957</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A379" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B379" s="9" t="s">
-        <v>959</v>
-      </c>
+      <c r="B379" s="2"/>
       <c r="C379" s="1" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A380" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B380" s="9" t="s">
-        <v>959</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="D380" s="1" t="s">
         <v>963</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B381" s="2"/>
-      <c r="C381" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D381" s="1" t="s">
-        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -9368,156 +9349,156 @@
     <hyperlink ref="D199" r:id="rId212"/>
     <hyperlink ref="D200" r:id="rId213"/>
     <hyperlink ref="D201" r:id="rId214"/>
-    <hyperlink ref="D203" r:id="rId215"/>
-    <hyperlink ref="D205" r:id="rId216"/>
-    <hyperlink ref="D206" r:id="rId217"/>
-    <hyperlink ref="D207" r:id="rId218"/>
-    <hyperlink ref="D208" r:id="rId219"/>
-    <hyperlink ref="D209" r:id="rId220"/>
-    <hyperlink ref="D210" r:id="rId221"/>
-    <hyperlink ref="D211" r:id="rId222"/>
-    <hyperlink ref="D212" r:id="rId223"/>
-    <hyperlink ref="D213" r:id="rId224"/>
-    <hyperlink ref="D214" r:id="rId225"/>
-    <hyperlink ref="D215" r:id="rId226"/>
-    <hyperlink ref="D216" r:id="rId227"/>
-    <hyperlink ref="D220" r:id="rId228"/>
-    <hyperlink ref="D221" r:id="rId229"/>
-    <hyperlink ref="D223" r:id="rId230"/>
-    <hyperlink ref="E223" r:id="rId231"/>
-    <hyperlink ref="D224" r:id="rId232"/>
-    <hyperlink ref="D225" r:id="rId233"/>
-    <hyperlink ref="D226" r:id="rId234"/>
-    <hyperlink ref="D227" r:id="rId235"/>
-    <hyperlink ref="D228" r:id="rId236"/>
-    <hyperlink ref="D236" r:id="rId237"/>
-    <hyperlink ref="D237" r:id="rId238"/>
-    <hyperlink ref="E237" r:id="rId239"/>
-    <hyperlink ref="D218" r:id="rId240"/>
-    <hyperlink ref="D238" r:id="rId241"/>
-    <hyperlink ref="D239" r:id="rId242"/>
-    <hyperlink ref="D240" r:id="rId243"/>
-    <hyperlink ref="D241" r:id="rId244"/>
-    <hyperlink ref="D242" r:id="rId245"/>
-    <hyperlink ref="D243" r:id="rId246"/>
-    <hyperlink ref="D244" r:id="rId247"/>
-    <hyperlink ref="D245" r:id="rId248"/>
-    <hyperlink ref="D246" r:id="rId249"/>
-    <hyperlink ref="D247" r:id="rId250"/>
-    <hyperlink ref="D248" r:id="rId251"/>
-    <hyperlink ref="D249" r:id="rId252"/>
-    <hyperlink ref="D250" r:id="rId253"/>
-    <hyperlink ref="D251" r:id="rId254"/>
-    <hyperlink ref="D252" r:id="rId255"/>
-    <hyperlink ref="D253" r:id="rId256"/>
-    <hyperlink ref="D254" r:id="rId257"/>
-    <hyperlink ref="D255" r:id="rId258"/>
-    <hyperlink ref="D256" r:id="rId259"/>
-    <hyperlink ref="D257" r:id="rId260"/>
-    <hyperlink ref="D258" r:id="rId261"/>
-    <hyperlink ref="D259" r:id="rId262"/>
-    <hyperlink ref="D260" r:id="rId263"/>
-    <hyperlink ref="D261" r:id="rId264"/>
-    <hyperlink ref="D262" r:id="rId265"/>
-    <hyperlink ref="D263" r:id="rId266"/>
-    <hyperlink ref="D264" r:id="rId267"/>
-    <hyperlink ref="D265" r:id="rId268"/>
-    <hyperlink ref="D266" r:id="rId269"/>
-    <hyperlink ref="D267" r:id="rId270"/>
-    <hyperlink ref="D268" r:id="rId271"/>
-    <hyperlink ref="D269" r:id="rId272"/>
-    <hyperlink ref="D270" r:id="rId273"/>
-    <hyperlink ref="E270" r:id="rId274"/>
-    <hyperlink ref="D271" r:id="rId275"/>
-    <hyperlink ref="D272" r:id="rId276"/>
-    <hyperlink ref="D273" r:id="rId277"/>
-    <hyperlink ref="D274" r:id="rId278"/>
-    <hyperlink ref="D275" r:id="rId279"/>
-    <hyperlink ref="D276" r:id="rId280"/>
-    <hyperlink ref="D277" r:id="rId281"/>
-    <hyperlink ref="D278" r:id="rId282"/>
-    <hyperlink ref="D279" r:id="rId283"/>
-    <hyperlink ref="D280" r:id="rId284"/>
-    <hyperlink ref="D281" r:id="rId285"/>
-    <hyperlink ref="D282" r:id="rId286"/>
-    <hyperlink ref="D283" r:id="rId287"/>
-    <hyperlink ref="D284" r:id="rId288"/>
-    <hyperlink ref="D285" r:id="rId289"/>
-    <hyperlink ref="D286" r:id="rId290"/>
-    <hyperlink ref="D287" r:id="rId291"/>
-    <hyperlink ref="D288" r:id="rId292"/>
-    <hyperlink ref="D289" r:id="rId293"/>
-    <hyperlink ref="D290" r:id="rId294"/>
-    <hyperlink ref="D291" r:id="rId295"/>
-    <hyperlink ref="D292" r:id="rId296"/>
-    <hyperlink ref="D293" r:id="rId297"/>
-    <hyperlink ref="D294" r:id="rId298"/>
-    <hyperlink ref="D295" r:id="rId299"/>
-    <hyperlink ref="D296" r:id="rId300"/>
-    <hyperlink ref="D297" r:id="rId301"/>
-    <hyperlink ref="E297" r:id="rId302"/>
-    <hyperlink ref="D298" r:id="rId303"/>
-    <hyperlink ref="D299" r:id="rId304"/>
-    <hyperlink ref="D300" r:id="rId305"/>
-    <hyperlink ref="D301" r:id="rId306"/>
-    <hyperlink ref="E301" r:id="rId307"/>
-    <hyperlink ref="D303" r:id="rId308"/>
-    <hyperlink ref="D304" r:id="rId309"/>
-    <hyperlink ref="D305" r:id="rId310"/>
-    <hyperlink ref="E305" r:id="rId311"/>
-    <hyperlink ref="D306" r:id="rId312"/>
-    <hyperlink ref="D307" r:id="rId313"/>
-    <hyperlink ref="D308" r:id="rId314"/>
-    <hyperlink ref="D309" r:id="rId315"/>
-    <hyperlink ref="D310" r:id="rId316"/>
-    <hyperlink ref="D311" r:id="rId317"/>
-    <hyperlink ref="D312" r:id="rId318"/>
-    <hyperlink ref="D313" r:id="rId319"/>
-    <hyperlink ref="D314" r:id="rId320"/>
-    <hyperlink ref="D315" r:id="rId321"/>
-    <hyperlink ref="D316" r:id="rId322"/>
-    <hyperlink ref="D317" r:id="rId323"/>
-    <hyperlink ref="D318" r:id="rId324"/>
-    <hyperlink ref="D319" r:id="rId325"/>
-    <hyperlink ref="D320" r:id="rId326"/>
-    <hyperlink ref="D321" r:id="rId327"/>
-    <hyperlink ref="D322" r:id="rId328"/>
-    <hyperlink ref="D323" r:id="rId329"/>
-    <hyperlink ref="D324" r:id="rId330"/>
-    <hyperlink ref="D325" r:id="rId331"/>
-    <hyperlink ref="D326" r:id="rId332"/>
-    <hyperlink ref="D327" r:id="rId333"/>
-    <hyperlink ref="D328" r:id="rId334"/>
-    <hyperlink ref="D329" r:id="rId335"/>
-    <hyperlink ref="D330" r:id="rId336"/>
-    <hyperlink ref="D331" r:id="rId337"/>
-    <hyperlink ref="D332" r:id="rId338"/>
-    <hyperlink ref="D333" r:id="rId339"/>
-    <hyperlink ref="D334" r:id="rId340"/>
-    <hyperlink ref="D335" r:id="rId341"/>
-    <hyperlink ref="D336" r:id="rId342"/>
-    <hyperlink ref="D337" r:id="rId343"/>
-    <hyperlink ref="D338" r:id="rId344"/>
-    <hyperlink ref="D339" r:id="rId345"/>
-    <hyperlink ref="D340" r:id="rId346"/>
-    <hyperlink ref="D341" r:id="rId347"/>
-    <hyperlink ref="D342" r:id="rId348"/>
-    <hyperlink ref="D343" r:id="rId349"/>
-    <hyperlink ref="D344" r:id="rId350"/>
-    <hyperlink ref="D345" r:id="rId351"/>
-    <hyperlink ref="D348" r:id="rId352"/>
-    <hyperlink ref="D349" r:id="rId353"/>
-    <hyperlink ref="D350" r:id="rId354"/>
-    <hyperlink ref="D351" r:id="rId355"/>
-    <hyperlink ref="D352" r:id="rId356"/>
-    <hyperlink ref="D353" r:id="rId357"/>
-    <hyperlink ref="D354" r:id="rId358"/>
-    <hyperlink ref="D355" r:id="rId359"/>
-    <hyperlink ref="D356" r:id="rId360"/>
-    <hyperlink ref="D357" r:id="rId361"/>
-    <hyperlink ref="D358" r:id="rId362"/>
-    <hyperlink ref="D360" r:id="rId363"/>
-    <hyperlink ref="D361" r:id="rId364"/>
+    <hyperlink ref="D202" r:id="rId215"/>
+    <hyperlink ref="D203" r:id="rId216"/>
+    <hyperlink ref="D204" r:id="rId217"/>
+    <hyperlink ref="D205" r:id="rId218"/>
+    <hyperlink ref="D206" r:id="rId219"/>
+    <hyperlink ref="D207" r:id="rId220"/>
+    <hyperlink ref="D208" r:id="rId221"/>
+    <hyperlink ref="D209" r:id="rId222"/>
+    <hyperlink ref="D210" r:id="rId223"/>
+    <hyperlink ref="D211" r:id="rId224"/>
+    <hyperlink ref="D212" r:id="rId225"/>
+    <hyperlink ref="D213" r:id="rId226"/>
+    <hyperlink ref="D214" r:id="rId227"/>
+    <hyperlink ref="D218" r:id="rId228"/>
+    <hyperlink ref="D219" r:id="rId229"/>
+    <hyperlink ref="D221" r:id="rId230"/>
+    <hyperlink ref="E221" r:id="rId231"/>
+    <hyperlink ref="D222" r:id="rId232"/>
+    <hyperlink ref="D223" r:id="rId233"/>
+    <hyperlink ref="D224" r:id="rId234"/>
+    <hyperlink ref="D225" r:id="rId235"/>
+    <hyperlink ref="D226" r:id="rId236"/>
+    <hyperlink ref="D234" r:id="rId237"/>
+    <hyperlink ref="D235" r:id="rId238"/>
+    <hyperlink ref="E235" r:id="rId239"/>
+    <hyperlink ref="D216" r:id="rId240"/>
+    <hyperlink ref="D236" r:id="rId241"/>
+    <hyperlink ref="D237" r:id="rId242"/>
+    <hyperlink ref="D238" r:id="rId243"/>
+    <hyperlink ref="D239" r:id="rId244"/>
+    <hyperlink ref="D240" r:id="rId245"/>
+    <hyperlink ref="D241" r:id="rId246"/>
+    <hyperlink ref="D242" r:id="rId247"/>
+    <hyperlink ref="D243" r:id="rId248"/>
+    <hyperlink ref="D244" r:id="rId249"/>
+    <hyperlink ref="D245" r:id="rId250"/>
+    <hyperlink ref="D246" r:id="rId251"/>
+    <hyperlink ref="D247" r:id="rId252"/>
+    <hyperlink ref="D248" r:id="rId253"/>
+    <hyperlink ref="D249" r:id="rId254"/>
+    <hyperlink ref="D250" r:id="rId255"/>
+    <hyperlink ref="D251" r:id="rId256"/>
+    <hyperlink ref="D252" r:id="rId257"/>
+    <hyperlink ref="D253" r:id="rId258"/>
+    <hyperlink ref="D254" r:id="rId259"/>
+    <hyperlink ref="D255" r:id="rId260"/>
+    <hyperlink ref="D256" r:id="rId261"/>
+    <hyperlink ref="D257" r:id="rId262"/>
+    <hyperlink ref="D258" r:id="rId263"/>
+    <hyperlink ref="D259" r:id="rId264"/>
+    <hyperlink ref="D260" r:id="rId265"/>
+    <hyperlink ref="D261" r:id="rId266"/>
+    <hyperlink ref="D262" r:id="rId267"/>
+    <hyperlink ref="D263" r:id="rId268"/>
+    <hyperlink ref="D264" r:id="rId269"/>
+    <hyperlink ref="D265" r:id="rId270"/>
+    <hyperlink ref="D266" r:id="rId271"/>
+    <hyperlink ref="D267" r:id="rId272"/>
+    <hyperlink ref="D268" r:id="rId273"/>
+    <hyperlink ref="E268" r:id="rId274"/>
+    <hyperlink ref="D269" r:id="rId275"/>
+    <hyperlink ref="D270" r:id="rId276"/>
+    <hyperlink ref="D271" r:id="rId277"/>
+    <hyperlink ref="D272" r:id="rId278"/>
+    <hyperlink ref="D273" r:id="rId279"/>
+    <hyperlink ref="D274" r:id="rId280"/>
+    <hyperlink ref="D275" r:id="rId281"/>
+    <hyperlink ref="D276" r:id="rId282"/>
+    <hyperlink ref="D277" r:id="rId283"/>
+    <hyperlink ref="D278" r:id="rId284"/>
+    <hyperlink ref="D279" r:id="rId285"/>
+    <hyperlink ref="D280" r:id="rId286"/>
+    <hyperlink ref="D281" r:id="rId287"/>
+    <hyperlink ref="D282" r:id="rId288"/>
+    <hyperlink ref="D283" r:id="rId289"/>
+    <hyperlink ref="D284" r:id="rId290"/>
+    <hyperlink ref="D285" r:id="rId291"/>
+    <hyperlink ref="D286" r:id="rId292"/>
+    <hyperlink ref="D287" r:id="rId293"/>
+    <hyperlink ref="D288" r:id="rId294"/>
+    <hyperlink ref="D289" r:id="rId295"/>
+    <hyperlink ref="D290" r:id="rId296"/>
+    <hyperlink ref="D291" r:id="rId297"/>
+    <hyperlink ref="D292" r:id="rId298"/>
+    <hyperlink ref="D293" r:id="rId299"/>
+    <hyperlink ref="D294" r:id="rId300"/>
+    <hyperlink ref="D295" r:id="rId301"/>
+    <hyperlink ref="E295" r:id="rId302"/>
+    <hyperlink ref="D296" r:id="rId303"/>
+    <hyperlink ref="D297" r:id="rId304"/>
+    <hyperlink ref="D298" r:id="rId305"/>
+    <hyperlink ref="D299" r:id="rId306"/>
+    <hyperlink ref="E299" r:id="rId307"/>
+    <hyperlink ref="D301" r:id="rId308"/>
+    <hyperlink ref="D302" r:id="rId309"/>
+    <hyperlink ref="D303" r:id="rId310"/>
+    <hyperlink ref="E303" r:id="rId311"/>
+    <hyperlink ref="D304" r:id="rId312"/>
+    <hyperlink ref="D305" r:id="rId313"/>
+    <hyperlink ref="D306" r:id="rId314"/>
+    <hyperlink ref="D307" r:id="rId315"/>
+    <hyperlink ref="D308" r:id="rId316"/>
+    <hyperlink ref="D309" r:id="rId317"/>
+    <hyperlink ref="D310" r:id="rId318"/>
+    <hyperlink ref="D311" r:id="rId319"/>
+    <hyperlink ref="D312" r:id="rId320"/>
+    <hyperlink ref="D313" r:id="rId321"/>
+    <hyperlink ref="D314" r:id="rId322"/>
+    <hyperlink ref="D315" r:id="rId323"/>
+    <hyperlink ref="D316" r:id="rId324"/>
+    <hyperlink ref="D317" r:id="rId325"/>
+    <hyperlink ref="D318" r:id="rId326"/>
+    <hyperlink ref="D319" r:id="rId327"/>
+    <hyperlink ref="D320" r:id="rId328"/>
+    <hyperlink ref="D321" r:id="rId329"/>
+    <hyperlink ref="D322" r:id="rId330"/>
+    <hyperlink ref="D323" r:id="rId331"/>
+    <hyperlink ref="D324" r:id="rId332"/>
+    <hyperlink ref="D325" r:id="rId333"/>
+    <hyperlink ref="D326" r:id="rId334"/>
+    <hyperlink ref="D327" r:id="rId335"/>
+    <hyperlink ref="D328" r:id="rId336"/>
+    <hyperlink ref="D329" r:id="rId337"/>
+    <hyperlink ref="D330" r:id="rId338"/>
+    <hyperlink ref="D331" r:id="rId339"/>
+    <hyperlink ref="D332" r:id="rId340"/>
+    <hyperlink ref="D333" r:id="rId341"/>
+    <hyperlink ref="D334" r:id="rId342"/>
+    <hyperlink ref="D335" r:id="rId343"/>
+    <hyperlink ref="D336" r:id="rId344"/>
+    <hyperlink ref="D337" r:id="rId345"/>
+    <hyperlink ref="D338" r:id="rId346"/>
+    <hyperlink ref="D339" r:id="rId347"/>
+    <hyperlink ref="D340" r:id="rId348"/>
+    <hyperlink ref="D341" r:id="rId349"/>
+    <hyperlink ref="D342" r:id="rId350"/>
+    <hyperlink ref="D343" r:id="rId351"/>
+    <hyperlink ref="D346" r:id="rId352"/>
+    <hyperlink ref="D347" r:id="rId353"/>
+    <hyperlink ref="D348" r:id="rId354"/>
+    <hyperlink ref="D349" r:id="rId355"/>
+    <hyperlink ref="D350" r:id="rId356"/>
+    <hyperlink ref="D351" r:id="rId357"/>
+    <hyperlink ref="D352" r:id="rId358"/>
+    <hyperlink ref="D353" r:id="rId359"/>
+    <hyperlink ref="D354" r:id="rId360"/>
+    <hyperlink ref="D355" r:id="rId361"/>
+    <hyperlink ref="D356" r:id="rId362"/>
+    <hyperlink ref="D358" r:id="rId363"/>
+    <hyperlink ref="D359" r:id="rId364"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId365"/>
